--- a/数智资源汇总整理.xlsx
+++ b/数智资源汇总整理.xlsx
@@ -4,15 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22552" windowHeight="11655"/>
+    <workbookView windowWidth="22552" windowHeight="11655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="网站工作本" sheetId="3" r:id="rId1"/>
     <sheet name="app" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">网站工作本!$A$1:$I$462</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">app!$A$1:$H$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">app!$A$2:$F$171</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5510" uniqueCount="2236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5184" uniqueCount="2124">
   <si>
     <t>网站名称</t>
   </si>
@@ -122,7 +123,7 @@
     <t>课程类</t>
   </si>
   <si>
-    <t>付费</t>
+    <t>部分付费</t>
   </si>
   <si>
     <t>更新不详</t>
@@ -4368,6 +4369,9 @@
   </si>
   <si>
     <t>林敏</t>
+  </si>
+  <si>
+    <t>付费</t>
   </si>
   <si>
     <t>龙凤海外少儿汉语</t>
@@ -5715,12 +5719,6 @@
     <t>研发单位</t>
   </si>
   <si>
-    <t>语种</t>
-  </si>
-  <si>
-    <t>注册信息</t>
-  </si>
-  <si>
     <t>网站</t>
   </si>
   <si>
@@ -5730,18 +5728,9 @@
     <t>印度教育科技公司Quizizz</t>
   </si>
   <si>
-    <t>英/汉/法/西/德/意/日/波/俄/土/越/葡/印/泰/阿塞拜疆/马来/菲律宾/哈塞克</t>
-  </si>
-  <si>
-    <t>邮箱、用户名、密码</t>
-  </si>
-  <si>
     <t>https://quizizz.com/</t>
   </si>
   <si>
-    <t>无法确认</t>
-  </si>
-  <si>
     <t>钉钉直播</t>
   </si>
   <si>
@@ -5796,12 +5785,6 @@
     <t>Shanghai Zhuyan Edu&amp;tech co., Ltd</t>
   </si>
   <si>
-    <t>俄文、泰文、简体中文、英文</t>
-  </si>
-  <si>
-    <t>手机号/邮箱/微信/facebook/google/苹果账户</t>
-  </si>
-  <si>
     <t>https://acechinese.cn</t>
   </si>
   <si>
@@ -5811,9 +5794,6 @@
     <t>Kubilay Saran</t>
   </si>
   <si>
-    <t>英文</t>
-  </si>
-  <si>
     <t>http://www.advanchinese.com</t>
   </si>
   <si>
@@ -5823,12 +5803,6 @@
     <t>Tripod Technology GmbH</t>
   </si>
   <si>
-    <t>俄文、德文、意大利文、日文、法文、简体中文、繁体中文、英文、葡萄牙文、西班牙文、韩文</t>
-  </si>
-  <si>
-    <t>脸书、谷歌、微博、微信、性别、头像、母语、兴趣、期望达到的水平</t>
-  </si>
-  <si>
     <t>https://tandem.zendesk.com/hc/en-us?mobile_site=true</t>
   </si>
   <si>
@@ -5838,12 +5812,6 @@
     <t>Chairman's Bao Ltd</t>
   </si>
   <si>
-    <t>英文、中文</t>
-  </si>
-  <si>
-    <t>用户名、密码、facebook</t>
-  </si>
-  <si>
     <t>https://www.thechairmansbao.com/contact-us</t>
   </si>
   <si>
@@ -5853,12 +5821,6 @@
     <t>Shanghai xiangai Education Technology</t>
   </si>
   <si>
-    <t>日文、英文、简体中文、泰文</t>
-  </si>
-  <si>
-    <t>邮箱、手机号或微信、facebook\google</t>
-  </si>
-  <si>
     <t>https://www.spkchinese.com</t>
   </si>
   <si>
@@ -5871,12 +5833,6 @@
     <t>北京华源智慧科技有限公司</t>
   </si>
   <si>
-    <t>英文、俄文、中文</t>
-  </si>
-  <si>
-    <t>微信、facebook或者手机号</t>
-  </si>
-  <si>
     <t>http://www.upanda.com</t>
   </si>
   <si>
@@ -5895,9 +5851,6 @@
     <t>Nemo Apps LLC</t>
   </si>
   <si>
-    <t>俄文、印度尼西亚文、德文、意大利文、日文、法文、泰文、瑞典文、简体中文、繁体中文、英文、荷兰文、葡萄牙文、西班牙文、韩文</t>
-  </si>
-  <si>
     <t>http://cn.nemoapps.com/support</t>
   </si>
   <si>
@@ -5907,9 +5860,6 @@
     <t>Simon Schmid</t>
   </si>
   <si>
-    <t>德文、意大利文、日文、法文、简体中文、英文、葡萄牙文、西班牙文、韩文</t>
-  </si>
-  <si>
     <t>https://www.twitter.com/learnjiapp</t>
   </si>
   <si>
@@ -5937,12 +5887,6 @@
     <t xml:space="preserve">Shanghai Yuxuan Information Technology </t>
   </si>
   <si>
-    <t>俄文、日文、法文、泰文、简体中文、英文、西班牙文、越南文、韩文</t>
-  </si>
-  <si>
-    <t>邮箱/手机号/微信/Google、facebook/wechat</t>
-  </si>
-  <si>
     <t>http://www.superchinese.com/site/protocol</t>
   </si>
   <si>
@@ -5952,9 +5896,6 @@
     <t>Innovative Language Learning USA LLC</t>
   </si>
   <si>
-    <t>选择语言：中文、英语、法语、德语、意大利语、日语、韩语、俄语、西班牙语、粤语、泰语、阿拉伯语、葡萄牙语、波斯语、波兰语、越南语、印尼语、菲律宾语、北印度语、土耳其语、荷兰语、瑞典语、挪威语、芬兰语、匈牙利语、希腊语、希伯来语、保加利亚语、斯瓦希里语、捷克语、丹麦语、南非荷兰语、罗马尼亚语、乌尔都语</t>
-  </si>
-  <si>
     <t>https://blog.innovativelanguage.com/frequently-asked-questions/</t>
   </si>
   <si>
@@ -5973,9 +5914,6 @@
     <t>Chineseskill Co., Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">日文、中文、英文 </t>
-  </si>
-  <si>
     <t>http://www.chinese-skill.com</t>
   </si>
   <si>
@@ -5985,12 +5923,6 @@
     <t>江苏文化天空有限责任公司</t>
   </si>
   <si>
-    <t>中文、英文</t>
-  </si>
-  <si>
-    <t>手机号、密码或者微信登录</t>
-  </si>
-  <si>
     <t>http://www.culturesky.com</t>
   </si>
   <si>
@@ -6000,12 +5932,6 @@
     <t xml:space="preserve">xie liuqiang </t>
   </si>
   <si>
-    <t>俄文、德文、日文、法文、简体中文、英文、西班牙文、韩文、葡萄牙文</t>
-  </si>
-  <si>
-    <t>昵称、邮箱、密码</t>
-  </si>
-  <si>
     <t>http://www.yxchinese.com</t>
   </si>
   <si>
@@ -6048,9 +5974,6 @@
     <t>ZHAO ZI LONG</t>
   </si>
   <si>
-    <t>简体中文、日文、英文</t>
-  </si>
-  <si>
     <t>HSK4 Grammar</t>
   </si>
   <si>
@@ -6072,9 +5995,6 @@
     <t>cortinajed Bonisa SL</t>
   </si>
   <si>
-    <t>简体中文、英文、葡萄牙文、西班牙文</t>
-  </si>
-  <si>
     <t>http://bonisa.com.es</t>
   </si>
   <si>
@@ -6093,9 +6013,6 @@
     <t>hand techinis</t>
   </si>
   <si>
-    <t>中文、丹麦文、乌克兰文、俄文、克罗地亚文、加泰罗尼亚文、匈牙利文、博克马尔文挪威文、印地文、印度尼西亚文、土耳其文、希伯来文、希腊文、德文、意大利文、捷克文、斯洛伐克文、日文、法文、波兰文、泰文、瑞典文、简体中文、繁体中文、罗马尼亚文、芬兰文、英文、荷兰文、葡萄牙文、西班牙文、越南文、阿拉伯语文、韩文、马来文</t>
-  </si>
-  <si>
     <t>http://www.handtechnics.com/support.html</t>
   </si>
   <si>
@@ -6120,9 +6037,6 @@
     <t>Praveenud Apiwattanahirun</t>
   </si>
   <si>
-    <t>中文、英文、泰语</t>
-  </si>
-  <si>
     <t>Daxiang HSK 5</t>
   </si>
   <si>
@@ -6174,9 +6088,6 @@
     <t>ouamass brahim</t>
   </si>
   <si>
-    <t>法文、英文、中文</t>
-  </si>
-  <si>
     <t>https://www.facebook.com/Toeic-Toef-Applications-299524097150909/</t>
   </si>
   <si>
@@ -6192,12 +6103,6 @@
     <t>FluentfLlix limited</t>
   </si>
   <si>
-    <t>日文、英文、西班牙文、韩文</t>
-  </si>
-  <si>
-    <t>邮箱 密码</t>
-  </si>
-  <si>
     <t>http://www.fluentu.com/support/</t>
   </si>
   <si>
@@ -6207,12 +6112,6 @@
     <t>Eggbun Education Co.,Ltd</t>
   </si>
   <si>
-    <t>中文、日文、韩文、英文、西班牙文、简体中文</t>
-  </si>
-  <si>
-    <t>姓名、学习需要，facebook google email</t>
-  </si>
-  <si>
     <t>http://www.eggbun-edu.com</t>
   </si>
   <si>
@@ -6234,9 +6133,6 @@
     <t>Han-sky</t>
   </si>
   <si>
-    <t>英文、简体中文</t>
-  </si>
-  <si>
     <t>https://www.han-sky.com</t>
   </si>
   <si>
@@ -6249,12 +6145,6 @@
     <t>广州五行教育科技有限公司</t>
   </si>
   <si>
-    <t>俄文、德文、日文、法文、简体中文、英文、西班牙文、阿拉伯文、韩文</t>
-  </si>
-  <si>
-    <t>填写性别、身份、感兴趣的主题、汉语水平测试后可用邮箱、微信、facebook登录</t>
-  </si>
-  <si>
     <t>http://www.5idea.com.cn</t>
   </si>
   <si>
@@ -6273,9 +6163,6 @@
     <t xml:space="preserve">XINGYAN CAO </t>
   </si>
   <si>
-    <t>中文、日文</t>
-  </si>
-  <si>
     <t>http://bzq188.lofter.com/post/1f478256_eeb85708</t>
   </si>
   <si>
@@ -6303,9 +6190,6 @@
     <t xml:space="preserve">LETS Limited </t>
   </si>
   <si>
-    <t>丹麦文、俄文、印度尼西亚文、土耳其文、希腊文、德文、意大利文、日文、法文、泰文、瑞典文、简体中文、繁体中文、芬兰文、英文、荷兰文、葡萄牙文、西班牙文、越南文、韩文、马来文</t>
-  </si>
-  <si>
     <t>http://www.lingo-apps.com</t>
   </si>
   <si>
@@ -6315,22 +6199,12 @@
     <t>Beijing Cocore Technology Co.,Ltd</t>
   </si>
   <si>
-    <t>手机号+验证码</t>
-  </si>
-  <si>
     <t>悟空识字</t>
   </si>
   <si>
     <t>宁波启点教育科技有限公司</t>
   </si>
   <si>
-    <t xml:space="preserve">丹麦文、俄文、博克马尔文挪威文、印度尼西亚文、土耳其文、希伯来文、希腊文、德文、意大利文、捷克文、日文、法文、波兰文、泰文、瑞典文、简体中文、繁体中文、芬兰文、英文、荷兰文、葡萄牙文、西班牙文、越南文、韩文、马来文
-</t>
-  </si>
-  <si>
-    <t>账号密码/微信</t>
-  </si>
-  <si>
     <t>http://www.gongfubb.com</t>
   </si>
   <si>
@@ -6340,12 +6214,6 @@
     <t>shenzhen Swap Internet Technology Co.,LTD</t>
   </si>
   <si>
-    <t>简体中文、英文</t>
-  </si>
-  <si>
-    <t>手机号码，但是一直无法注册和登录</t>
-  </si>
-  <si>
     <t>https://www.3wyc.com</t>
   </si>
   <si>
@@ -6379,9 +6247,6 @@
     <t>咪咕数字传媒有限公司</t>
   </si>
   <si>
-    <t>简体中文</t>
-  </si>
-  <si>
     <t>http://lingxi.10086.cn/wap/</t>
   </si>
   <si>
@@ -6391,12 +6256,6 @@
     <t>HELLOTALK FOREIGN LANGUAGE EXCHANGE LEARNING TALK CHAT APP</t>
   </si>
   <si>
-    <t>世界语、丹麦文、俄文、加泰罗尼亚文、印度尼西亚文、土耳其文、德文、意大利文、日文、法文、波斯文、泰文、简体中文、繁体中文、英文、葡萄牙文、西班牙文、越南文、阿拉伯文、韩文</t>
-  </si>
-  <si>
-    <t>邮箱、微信、facebook</t>
-  </si>
-  <si>
     <t>http://support.hellotalk.com</t>
   </si>
   <si>
@@ -6406,9 +6265,6 @@
     <t xml:space="preserve"> Studycat limited</t>
   </si>
   <si>
-    <t>丹麦文、俄文、博克马尔文挪威文、印度尼西亚文、土耳其文、希腊文、德文、意大利文、日文、法文、泰文、瑞典文、简体中文、繁体中文、芬兰文、英文、荷兰文、葡萄牙文、西班牙文、越南文、韩文、马来文</t>
-  </si>
-  <si>
     <t>https://studycat.com/support/ios</t>
   </si>
   <si>
@@ -6418,9 +6274,6 @@
     <t>GIANT BALLIOON DIGITAL,LLC</t>
   </si>
   <si>
-    <t>英文、中文、西班牙语</t>
-  </si>
-  <si>
     <t>http://gtbln.com/support</t>
   </si>
   <si>
@@ -6448,9 +6301,6 @@
     <t>西安新月软件公司</t>
   </si>
   <si>
-    <t>手机号、密码或者微信、QQ、微博</t>
-  </si>
-  <si>
     <t>http://www.nm29.com</t>
   </si>
   <si>
@@ -6460,9 +6310,6 @@
     <t>iTranslate GmnH</t>
   </si>
   <si>
-    <t>丹麦文、俄文、博克马尔文挪威文、印地文、印度尼西亚文、土耳其文、希腊文、德文、意大利文、日文、法文、波兰文、泰文、瑞典文、简体中文、繁体中文、芬兰文、英文、荷兰文、葡萄牙文、西班牙文、阿拉伯文、韩文、马来文</t>
-  </si>
-  <si>
     <t>https://www.itranslate.com/support/</t>
   </si>
   <si>
@@ -6472,12 +6319,6 @@
     <t xml:space="preserve">Never Corp </t>
   </si>
   <si>
-    <t>中文、英文、韩文、日文</t>
-  </si>
-  <si>
-    <t>Line facebook</t>
-  </si>
-  <si>
     <t>https://help.naver.com</t>
   </si>
   <si>
@@ -6487,9 +6328,6 @@
     <t>PROLOG Limited</t>
   </si>
   <si>
-    <t>中文、俄文、希伯来文、德文、意大利文、日文、法文、英文、葡萄牙文、西班牙文</t>
-  </si>
-  <si>
     <t>http://n42.tech/chinese</t>
   </si>
   <si>
@@ -6526,13 +6364,6 @@
     <t>SayHI,LLC</t>
   </si>
   <si>
-    <t>南非语、阿拉伯语、孟加拉语、波斯尼亚语、保加利亚语、中文（粤语-传统）、中文（普通话）、加泰罗尼亚语、克罗地亚语、捷克语、丹麦语、荷兰语、英语、爱沙尼亚语、斐济语、菲律宾语、芬兰语、法语、德语、希腊语、海地克里奥尔语、希伯来语、印地语、苗语、匈牙利语、印度尼西亚语、意大利语、日语、韩语、拉脱维亚语、立陶宛语、马达加斯加语、马来语、马耳他语、挪威语、波斯语、波兰语、葡萄牙语、罗马尼亚语、俄语、塞尔维亚语、斯洛伐克语、斯洛文尼亚语、萨摩亚语、西班牙语、斯瓦希里语、瑞典语、泰米尔语、泰语、汤加语、土耳其语、乌克兰语，乌尔都语，越南语，威尔士语
-+支持以下语言的方言：
-阿拉伯语：阿尔及利亚、巴林、埃及、伊拉克、约旦、科威特、利比亚、摩洛哥、阿曼、巴勒斯坦、卡塔尔、沙特阿拉伯、突尼斯、阿联酋、也门
-英语：澳大利亚、加拿大、印度、新西兰、南非、英国、美国  法语：加拿大、法国  意大利语：意大利，瑞士   普通话：中国(简体中文）、台湾(繁体中文）
-葡萄牙语：巴西、葡萄牙  西班牙语：阿根廷、玻利维亚、哥伦比亚、哥斯达黎加、多米尼加共和国、萨尔瓦多、危地马拉、洪都拉斯、墨西哥、尼加拉瓜、巴拿马、巴拉圭、秘鲁、波多黎各、西班牙、乌拉圭、美国、委内瑞拉</t>
-  </si>
-  <si>
     <t>https://www.sayhitranslate.com</t>
   </si>
   <si>
@@ -6542,9 +6373,6 @@
     <t>商务印书馆</t>
   </si>
   <si>
-    <t>拉脱维亚文、简体中文</t>
-  </si>
-  <si>
     <t>https://shangdii.cn</t>
   </si>
   <si>
@@ -6554,9 +6382,6 @@
     <t>Almas lnc</t>
   </si>
   <si>
-    <t>英文、蒙语</t>
-  </si>
-  <si>
     <t>http://www.mongolfont.com</t>
   </si>
   <si>
@@ -6566,9 +6391,6 @@
     <t>蒙古蒙科立软件有限责任公司</t>
   </si>
   <si>
-    <t>英文、中文、蒙语、新蒙语</t>
-  </si>
-  <si>
     <t>http://www.menksoft.com/site/alias__menkcms/2830/Default.aspx</t>
   </si>
   <si>
@@ -6578,9 +6400,6 @@
     <t>cai yaqing</t>
   </si>
   <si>
-    <t>简体中文、英语、法语、德语、韩语、日语、俄罗斯语、西班牙语、泰语、阿拉伯语、葡萄牙语、意大利语、粤话、保加利亚话、加泰罗尼亚语、繁体中文、捷克话、丹麦语、荷兰语、爱沙尼亚语、芬兰语、希腊语、希伯来语、印地语、匈牙利话、印度尼西亚话、克林贡语、拉脱维亚语、立陶宛话、马来语、马耳他话、挪威语、波斯话、罗马尼亚语、斯洛伐克话、斯洛文尼亚话、瑞典语、土耳其语、乌克兰话、乌尔都语、越南话、威尔士话40种语言</t>
-  </si>
-  <si>
     <t>http://m.3g.qq.com/wbread/copage/singleguest?lp=0,0,5,0,6&amp;id=weibolight2470</t>
   </si>
   <si>
@@ -6590,15 +6409,9 @@
     <t>Jafar Najafov</t>
   </si>
   <si>
-    <t>法语、简体中文、英文</t>
-  </si>
-  <si>
     <t>德语汉语词典+</t>
   </si>
   <si>
-    <t>德文、简体中文、英文</t>
-  </si>
-  <si>
     <t>大象中文</t>
   </si>
   <si>
@@ -6608,12 +6421,6 @@
     <t>云南大象文化网络信息有限公司</t>
   </si>
   <si>
-    <t>泰语、简体中文、英语</t>
-  </si>
-  <si>
-    <t>账号、密码、邮箱、推荐码（可选）</t>
-  </si>
-  <si>
     <t>https://www.elephantcn.com</t>
   </si>
   <si>
@@ -6623,12 +6430,6 @@
     <t>Baudu(China)Co,Ltd</t>
   </si>
   <si>
-    <t>简体中文、英语</t>
-  </si>
-  <si>
-    <t>手机、邮箱、百度账号/微信、微博、QQ</t>
-  </si>
-  <si>
     <t>http://hanyu.baidu.com</t>
   </si>
   <si>
@@ -6636,12 +6437,6 @@
   </si>
   <si>
     <t xml:space="preserve">Beijing Baidu Netcom Science&amp;Technology </t>
-  </si>
-  <si>
-    <t>英文、简体中文、繁体中文</t>
-  </si>
-  <si>
-    <t>学历水平、学习目的、兴趣</t>
   </si>
   <si>
     <t xml:space="preserve">https://fanyi.baidu.com </t>
@@ -6690,18 +6485,12 @@
 </t>
   </si>
   <si>
-    <t>俄文, 英文, 西班牙文</t>
-  </si>
-  <si>
     <t>速学汉语拼音</t>
   </si>
   <si>
     <t xml:space="preserve">Majestech LLC </t>
   </si>
   <si>
-    <t>日文, 简体中文, 繁体中文, 英文</t>
-  </si>
-  <si>
     <t>http://majestech.co.jp/app/chinese-pinyin-game/</t>
   </si>
   <si>
@@ -6720,12 +6509,6 @@
     <t xml:space="preserve">Jiangxi Miisi Technology Co., Ltd. </t>
   </si>
   <si>
-    <t>简体中文, 英文</t>
-  </si>
-  <si>
-    <t>微信、Facebook、twitter账号</t>
-  </si>
-  <si>
     <t>http://www.magichinese.com/</t>
   </si>
   <si>
@@ -6735,21 +6518,12 @@
     <t xml:space="preserve">Heyni Technology Corp. </t>
   </si>
   <si>
-    <t>简体中文, 繁体中文, 英文</t>
-  </si>
-  <si>
-    <t>名字、性别、出生日期、邮箱、密码</t>
-  </si>
-  <si>
     <t>https://www.heynitalk.com/</t>
   </si>
   <si>
     <t>Heyni Talk</t>
   </si>
   <si>
-    <t>学习目的、名字、性别、出生日期、邮箱、密码</t>
-  </si>
-  <si>
     <t>Chinese character by wcc</t>
   </si>
   <si>
@@ -6768,19 +6542,12 @@
     <t xml:space="preserve">Learn Mandarin Chinese 5,000 Words - FlashCards &amp; Games </t>
   </si>
   <si>
-    <t xml:space="preserve">
-日文, 英文</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chinese Flash Cards - Kids learn Mandarin Chinese quick with audio &amp; video flashcards! </t>
   </si>
   <si>
     <t>eFlashApps, LLC</t>
   </si>
   <si>
-    <t>英语</t>
-  </si>
-  <si>
     <t>http://www.babyflashcards.com/</t>
   </si>
   <si>
@@ -6793,9 +6560,6 @@
     <t>Yaroslav Mironov</t>
   </si>
   <si>
-    <t>简/繁体中文,英文,德语,法语,意大利语,日语,韩语,泰语,俄语,越南语等</t>
-  </si>
-  <si>
     <t>http://www.havefunlearnchinese.com/</t>
   </si>
   <si>
@@ -6814,9 +6578,6 @@
     <t xml:space="preserve">SOOL HO </t>
   </si>
   <si>
-    <t>可离线使用</t>
-  </si>
-  <si>
     <t xml:space="preserve">http://easylearnlanguageapps.wordpress.com </t>
   </si>
   <si>
@@ -6847,12 +6608,6 @@
     <t xml:space="preserve">LastThink </t>
   </si>
   <si>
-    <t>Asu (Tanzania), Zarma, 乌兹别克文, 乌尔都文, 亚美尼亚文, 依地文, 俄文, 南非荷兰文, 印地文, 奥里雅文, 宗喀语, 巴斯克文, 干达文, 班巴拉文, 白俄罗斯文, 祖鲁文, 约鲁巴文, 维吾尔文, 英文, 豪萨文, 车臣文, 阿布哈西亚文, 阿萨姆文, 马其顿文</t>
-  </si>
-  <si>
-    <t>Apple ID</t>
-  </si>
-  <si>
     <t>http://lastthink.com/</t>
   </si>
   <si>
@@ -6862,10 +6617,6 @@
     <t>trainchinese B.V.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-俄文, 英文, 西班牙文</t>
-  </si>
-  <si>
     <t>PinyinTrainer by trainchinese</t>
   </si>
   <si>
@@ -6887,13 +6638,6 @@
     <t>xiongjie huang</t>
   </si>
   <si>
-    <t xml:space="preserve">
-俄文, 德文, 日文, 法文, 泰文, 简体中文, 英文, 西班牙文, 越南文, 阿拉伯文, 韩文</t>
-  </si>
-  <si>
-    <t>微信/邮箱、验证码、密码</t>
-  </si>
-  <si>
     <t>https://vochina.com/home</t>
   </si>
   <si>
@@ -6903,9 +6647,6 @@
     <t xml:space="preserve">Microsoft Corporation </t>
   </si>
   <si>
-    <t>microsoft/linkedln/facebook账号</t>
-  </si>
-  <si>
     <t>http://learnchinese.mtutor.engkoo.com/learnchinese/index.html</t>
   </si>
   <si>
@@ -6918,12 +6659,6 @@
     <t xml:space="preserve">Duolingo, Inc </t>
   </si>
   <si>
-    <t>乌克兰文, 俄文, 匈牙利文, 印地文, 印度尼西亚文, 土耳其文, 希腊文, 德文, 意大利文, 捷克文, 日文, 法文, 波兰文, 泰文, 简体中文, 繁体中文, 罗马尼亚文, 英文, 荷兰文, 葡萄牙文, 西班牙文, 越南文, 阿拉伯文, 韩文</t>
-  </si>
-  <si>
-    <t>微信、邮箱、手机号</t>
-  </si>
-  <si>
     <t>http://www.duolingo.cn/info</t>
   </si>
   <si>
@@ -6933,9 +6668,6 @@
     <t xml:space="preserve">PLANB LABS OU </t>
   </si>
   <si>
-    <t>facebook、google、email</t>
-  </si>
-  <si>
     <t>https://languagedrops.com/</t>
   </si>
   <si>
@@ -6957,18 +6689,12 @@
     <t xml:space="preserve">ZHONGLI CHEN </t>
   </si>
   <si>
-    <t>微信、QQ</t>
-  </si>
-  <si>
     <t>http://www.happy-learn.com/</t>
   </si>
   <si>
     <t>Written Cinese with Dictionary</t>
   </si>
   <si>
-    <t>丹麦文, 乌克兰文, 俄文, 加泰罗尼亚文, 匈牙利文, 博克马尔文挪威文, 印度尼西亚文, 土耳其文, 希伯来文, 希腊文, 德语, 意大利语, 捷克文, 斯洛伐克文, 日语, 法语, 波兰文, 泰文, 瑞典文, 简体中文, 繁体中文, 罗马尼亚文, 芬兰文, 英语, 荷兰文, 葡萄牙文, 西班牙语, 越南文, 阿拉伯文, 韩语, 马来文</t>
-  </si>
-  <si>
     <t>https://www.writtenchinese.com/</t>
   </si>
   <si>
@@ -6981,13 +6707,6 @@
     <t xml:space="preserve">Funnybean Technology Co. , Ltd </t>
   </si>
   <si>
-    <t xml:space="preserve"> 
-中文, 俄文, 日语, 泰文, 简体中文, 英语, 西班牙语, 阿拉伯文，韩语</t>
-  </si>
-  <si>
-    <t>手机号/Beanlings/Facebook/wechat/weibo账号</t>
-  </si>
-  <si>
     <t>http://www.fuunybean.com/</t>
   </si>
   <si>
@@ -6997,9 +6716,6 @@
     <t>Learn Chinese Mandarin Pinyin Word Baby FlashCard</t>
   </si>
   <si>
-    <t>丹麦文, 俄文, 印度尼西亚文, 土耳其文, 希腊文, 德语, 意大利语, 日语, 法语, 泰文, 瑞典文, 简体中文, 繁体中文, 芬兰文, 英语, 荷兰文, 葡萄牙文, 西班牙语, 越南文, 韩语, 马来文</t>
-  </si>
-  <si>
     <t>Du Chinese:Read&amp;Learn Chinese</t>
   </si>
   <si>
@@ -7042,12 +6758,6 @@
     <t>ChineseSkill：外国人学汉语必备助手</t>
   </si>
   <si>
-    <t>俄/德/日/法语/繁体中文/英语/葡/西/越/韩</t>
-  </si>
-  <si>
-    <t>邮箱/facebook账号/Google账号/用户名、密码</t>
-  </si>
-  <si>
     <t>http://www.cslpod.com</t>
   </si>
   <si>
@@ -7057,24 +6767,12 @@
     <t>HelloChinese Technology Co., Ltd.</t>
   </si>
   <si>
-    <t>简体中文，英语</t>
-  </si>
-  <si>
-    <t>邮箱、密码</t>
-  </si>
-  <si>
     <t>http://www.hellochinese.cc/contact.html</t>
   </si>
   <si>
     <t>Quizlet Inc</t>
   </si>
   <si>
-    <t>俄文, 印度尼西亚文, 土耳其文, 德文, 意大利文, 日文, 法文, 波兰文, 简体中文, 繁体中文, 英文, 荷兰文, 葡萄牙文, 西班牙文, 越南文, 韩文</t>
-  </si>
-  <si>
-    <t>facebook账号/google账号/邮箱、出生日期、用户名、密码</t>
-  </si>
-  <si>
     <t>https://quizlet.com/zh-cn</t>
   </si>
   <si>
@@ -7087,12 +6785,6 @@
     <t>中和世纪文化传播（北京）有限公司</t>
   </si>
   <si>
-    <t>英语，韩语</t>
-  </si>
-  <si>
-    <t>Facebook账号/微信账号/Twitter账号/手机号、密码</t>
-  </si>
-  <si>
     <t>https://www.yiyahanyu.com/html/download.html</t>
   </si>
   <si>
@@ -7105,12 +6797,6 @@
     <t>北京华语时代文化传媒有限公司</t>
   </si>
   <si>
-    <t>简体中文，繁体中文，英语</t>
-  </si>
-  <si>
-    <t>facebook账号/Google账号/微信账号/微博账号/QQ账号/手机号/邮箱、密码</t>
-  </si>
-  <si>
     <t>SuperTest-汉语水平考试学习应用</t>
   </si>
   <si>
@@ -7120,12 +6806,6 @@
     <t>上海语轩信息技术有限公司</t>
   </si>
   <si>
-    <t>俄文，日文，泰文，简体中文，英文，越南文，韩文</t>
-  </si>
-  <si>
-    <t>facebook账号/Google账号/微信账号/手机号/邮箱、密码</t>
-  </si>
-  <si>
     <t>http://www.hskonline.com/</t>
   </si>
   <si>
@@ -7135,22 +6815,12 @@
     <t>planb labs ou</t>
   </si>
   <si>
-    <t>韩语，日语，中文/广东话，西班牙文/拉美西班牙文，法语，德语，荷兰语，意大利语，俄语，葡萄牙语（EU）/巴西葡萄牙语，希伯来语，阿拉伯语，土耳其语，他加禄语，越南语，印尼，丹麦语，瑞典语，挪威语，冰岛，匈牙利语，世界语，印地文，美式英语/英式英语</t>
-  </si>
-  <si>
-    <t>facebook账号/Google账号/邮箱、用户名、密码</t>
-  </si>
-  <si>
     <t>HelloChinese</t>
   </si>
   <si>
     <t>HelloChinese Technology co.,Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-俄文, 德文, 日文, 法文, 泰文, 英文, 葡萄牙文, 西班牙文, 越南文, 韩文</t>
-  </si>
-  <si>
     <t>http://www.hellochinese.cc/</t>
   </si>
   <si>
@@ -7163,9 +6833,6 @@
     <t xml:space="preserve">Chinesepod Limited </t>
   </si>
   <si>
-    <t>英/汉</t>
-  </si>
-  <si>
     <t>https://chinesepod.com/</t>
   </si>
   <si>
@@ -7175,18 +6842,9 @@
     <t> Jenni AI </t>
   </si>
   <si>
-    <t>邮箱、账号、密码</t>
-  </si>
-  <si>
     <t>https://tinywow.com/</t>
   </si>
   <si>
-    <t>中文</t>
-  </si>
-  <si>
-    <t>手机号、密码、验证码</t>
-  </si>
-  <si>
     <t xml:space="preserve">HSK GO </t>
   </si>
   <si>
@@ -7202,9 +6860,6 @@
     <t>复旦大学国际文化交流学院/复旦大学-汉考国际创新研究基地</t>
   </si>
   <si>
-    <t>英、日、韩、俄、泰、法、越</t>
-  </si>
-  <si>
     <t>https://www.hskcert.com/</t>
   </si>
   <si>
@@ -7220,9 +6875,6 @@
     <t>深圳市章鱼时代科技发展有限公司</t>
   </si>
   <si>
-    <t>14种语言</t>
-  </si>
-  <si>
     <t>https://www.chinesia.com.cn/</t>
   </si>
   <si>
@@ -7230,6 +6882,9 @@
   </si>
   <si>
     <t>Wo Hui HSK Courses</t>
+  </si>
+  <si>
+    <t>无法确认</t>
   </si>
 </sst>
 </file>
@@ -7458,20 +7113,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="6"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11.5"/>
-      <color rgb="FF515571"/>
+      <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF515571"/>
-      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -7493,27 +7151,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF474747"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11.6"/>
       <color rgb="FF4C6072"/>
       <name val="Noto Sans SC"/>
@@ -7523,6 +7160,24 @@
       <sz val="11.6"/>
       <color rgb="FF224A68"/>
       <name val="Noto Sans SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF515571"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF515571"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF474747"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -8415,7 +8070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I462"/>
   <sheetFormatPr defaultColWidth="9.60176991150442" defaultRowHeight="21" customHeight="1"/>
   <cols>
@@ -8459,7 +8114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:9">
+    <row r="2" hidden="1" customHeight="1" spans="1:9">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -8488,7 +8143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="3" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A3" s="18" t="s">
         <v>18</v>
       </c>
@@ -8546,7 +8201,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:9">
+    <row r="5" hidden="1" customHeight="1" spans="1:9">
       <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
@@ -8604,7 +8259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="7" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>42</v>
       </c>
@@ -8633,7 +8288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" s="19" customFormat="1" customHeight="1" spans="1:9">
+    <row r="8" s="19" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A8" s="19" t="s">
         <v>47</v>
       </c>
@@ -8749,7 +8404,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:9">
+    <row r="12" hidden="1" customHeight="1" spans="1:9">
       <c r="A12" s="4" t="s">
         <v>65</v>
       </c>
@@ -8807,7 +8462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:9">
+    <row r="14" hidden="1" customHeight="1" spans="1:9">
       <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
@@ -8836,7 +8491,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" hidden="1" customHeight="1" spans="1:9">
       <c r="A15" s="4" t="s">
         <v>77</v>
       </c>
@@ -8865,7 +8520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="16" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A16" s="18" t="s">
         <v>81</v>
       </c>
@@ -9126,7 +8781,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="25" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A25" s="18" t="s">
         <v>116</v>
       </c>
@@ -9155,7 +8810,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:9">
+    <row r="26" hidden="1" customHeight="1" spans="1:9">
       <c r="A26" s="4" t="s">
         <v>120</v>
       </c>
@@ -9184,7 +8839,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:9">
+    <row r="27" hidden="1" customHeight="1" spans="1:9">
       <c r="A27" s="4" t="s">
         <v>124</v>
       </c>
@@ -9242,7 +8897,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="29" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A29" s="18" t="s">
         <v>133</v>
       </c>
@@ -9271,7 +8926,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="30" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A30" s="18" t="s">
         <v>137</v>
       </c>
@@ -9329,7 +8984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="32" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A32" s="18" t="s">
         <v>145</v>
       </c>
@@ -9358,7 +9013,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:9">
+    <row r="33" hidden="1" customHeight="1" spans="1:9">
       <c r="A33" s="4" t="s">
         <v>148</v>
       </c>
@@ -9503,7 +9158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="38" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A38" s="18" t="s">
         <v>170</v>
       </c>
@@ -9735,7 +9390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:9">
+    <row r="46" hidden="1" customHeight="1" spans="1:9">
       <c r="A46" s="4" t="s">
         <v>201</v>
       </c>
@@ -9764,7 +9419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:9">
+    <row r="47" hidden="1" customHeight="1" spans="1:9">
       <c r="A47" s="4" t="s">
         <v>205</v>
       </c>
@@ -9851,7 +9506,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:9">
+    <row r="50" hidden="1" customHeight="1" spans="1:9">
       <c r="A50" s="4" t="s">
         <v>218</v>
       </c>
@@ -9909,7 +9564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:9">
+    <row r="52" hidden="1" customHeight="1" spans="1:9">
       <c r="A52" s="4" t="s">
         <v>225</v>
       </c>
@@ -9938,7 +9593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:9">
+    <row r="53" hidden="1" customHeight="1" spans="1:9">
       <c r="A53" s="4" t="s">
         <v>229</v>
       </c>
@@ -9967,7 +9622,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:9">
+    <row r="54" hidden="1" customHeight="1" spans="1:9">
       <c r="A54" s="4" t="s">
         <v>233</v>
       </c>
@@ -9996,7 +9651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:9">
+    <row r="55" hidden="1" customHeight="1" spans="1:9">
       <c r="A55" s="4" t="s">
         <v>237</v>
       </c>
@@ -10054,7 +9709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:9">
+    <row r="57" hidden="1" customHeight="1" spans="1:9">
       <c r="A57" s="4" t="s">
         <v>245</v>
       </c>
@@ -10112,7 +9767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:9">
+    <row r="59" hidden="1" customHeight="1" spans="1:9">
       <c r="A59" s="4" t="s">
         <v>253</v>
       </c>
@@ -10141,7 +9796,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:9">
+    <row r="60" hidden="1" customHeight="1" spans="1:9">
       <c r="A60" s="4" t="s">
         <v>257</v>
       </c>
@@ -10170,7 +9825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:9">
+    <row r="61" hidden="1" customHeight="1" spans="1:9">
       <c r="A61" s="4" t="s">
         <v>261</v>
       </c>
@@ -10257,7 +9912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:9">
+    <row r="64" hidden="1" customHeight="1" spans="1:9">
       <c r="A64" s="4" t="s">
         <v>273</v>
       </c>
@@ -10576,7 +10231,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:9">
+    <row r="75" hidden="1" customHeight="1" spans="1:9">
       <c r="A75" s="4" t="s">
         <v>315</v>
       </c>
@@ -10605,7 +10260,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:9">
+    <row r="76" hidden="1" customHeight="1" spans="1:9">
       <c r="A76" s="4" t="s">
         <v>319</v>
       </c>
@@ -11069,7 +10724,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="92" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A92" s="2" t="s">
         <v>370</v>
       </c>
@@ -11098,7 +10753,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:9">
+    <row r="93" hidden="1" customHeight="1" spans="1:9">
       <c r="A93" s="4" t="s">
         <v>374</v>
       </c>
@@ -11156,7 +10811,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:9">
+    <row r="95" hidden="1" customHeight="1" spans="1:9">
       <c r="A95" s="4" t="s">
         <v>382</v>
       </c>
@@ -11185,7 +10840,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:9">
+    <row r="96" hidden="1" customHeight="1" spans="1:9">
       <c r="A96" s="4" t="s">
         <v>386</v>
       </c>
@@ -11214,7 +10869,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="1:9">
+    <row r="97" hidden="1" customHeight="1" spans="1:9">
       <c r="A97" s="4" t="s">
         <v>390</v>
       </c>
@@ -11388,7 +11043,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:9">
+    <row r="103" hidden="1" customHeight="1" spans="1:9">
       <c r="A103" s="4" t="s">
         <v>412</v>
       </c>
@@ -11562,7 +11217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:9">
+    <row r="109" hidden="1" customHeight="1" spans="1:9">
       <c r="A109" s="4" t="s">
         <v>435</v>
       </c>
@@ -11620,7 +11275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:9">
+    <row r="111" hidden="1" customHeight="1" spans="1:9">
       <c r="A111" s="4" t="s">
         <v>442</v>
       </c>
@@ -11649,7 +11304,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="112" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A112" s="18" t="s">
         <v>446</v>
       </c>
@@ -11765,7 +11420,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="1:9">
+    <row r="116" hidden="1" customHeight="1" spans="1:9">
       <c r="A116" s="4" t="s">
         <v>463</v>
       </c>
@@ -11794,7 +11449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" customHeight="1" spans="1:9">
+    <row r="117" hidden="1" customHeight="1" spans="1:9">
       <c r="A117" s="4" t="s">
         <v>467</v>
       </c>
@@ -11823,7 +11478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" customHeight="1" spans="1:9">
+    <row r="118" hidden="1" customHeight="1" spans="1:9">
       <c r="A118" s="4" t="s">
         <v>471</v>
       </c>
@@ -11852,7 +11507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="1:9">
+    <row r="119" hidden="1" customHeight="1" spans="1:9">
       <c r="A119" s="4" t="s">
         <v>475</v>
       </c>
@@ -11881,7 +11536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" customHeight="1" spans="1:9">
+    <row r="120" hidden="1" customHeight="1" spans="1:9">
       <c r="A120" s="4" t="s">
         <v>479</v>
       </c>
@@ -11910,7 +11565,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" customHeight="1" spans="1:9">
+    <row r="121" hidden="1" customHeight="1" spans="1:9">
       <c r="A121" s="4" t="s">
         <v>483</v>
       </c>
@@ -11968,7 +11623,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" customHeight="1" spans="1:9">
+    <row r="123" hidden="1" customHeight="1" spans="1:9">
       <c r="A123" s="4" t="s">
         <v>491</v>
       </c>
@@ -12171,7 +11826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="1:9">
+    <row r="130" hidden="1" customHeight="1" spans="1:9">
       <c r="A130" s="4" t="s">
         <v>517</v>
       </c>
@@ -12200,7 +11855,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="1:9">
+    <row r="131" hidden="1" customHeight="1" spans="1:9">
       <c r="A131" s="4" t="s">
         <v>521</v>
       </c>
@@ -12229,7 +11884,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="1:9">
+    <row r="132" hidden="1" customHeight="1" spans="1:9">
       <c r="A132" s="4" t="s">
         <v>525</v>
       </c>
@@ -12258,7 +11913,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="1:9">
+    <row r="133" hidden="1" customHeight="1" spans="1:9">
       <c r="A133" s="4" t="s">
         <v>530</v>
       </c>
@@ -12316,7 +11971,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="1:9">
+    <row r="135" hidden="1" customHeight="1" spans="1:9">
       <c r="A135" s="4" t="s">
         <v>539</v>
       </c>
@@ -12896,7 +12551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="155" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A155" s="18" t="s">
         <v>602</v>
       </c>
@@ -12925,7 +12580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="156" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A156" s="18" t="s">
         <v>606</v>
       </c>
@@ -12954,7 +12609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="157" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A157" s="2" t="s">
         <v>610</v>
       </c>
@@ -13012,7 +12667,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="1:9">
+    <row r="159" hidden="1" customHeight="1" spans="1:9">
       <c r="A159" s="4" t="s">
         <v>618</v>
       </c>
@@ -13041,7 +12696,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" customHeight="1" spans="1:9">
+    <row r="160" hidden="1" customHeight="1" spans="1:9">
       <c r="A160" s="4" t="s">
         <v>623</v>
       </c>
@@ -13070,7 +12725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="1:9">
+    <row r="161" hidden="1" customHeight="1" spans="1:9">
       <c r="A161" s="4" t="s">
         <v>627</v>
       </c>
@@ -13157,7 +12812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="1:9">
+    <row r="164" hidden="1" customHeight="1" spans="1:9">
       <c r="A164" s="4" t="s">
         <v>639</v>
       </c>
@@ -13186,7 +12841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="1:9">
+    <row r="165" hidden="1" customHeight="1" spans="1:9">
       <c r="A165" s="4" t="s">
         <v>643</v>
       </c>
@@ -13331,7 +12986,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="170" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A170" s="18" t="s">
         <v>662</v>
       </c>
@@ -13360,7 +13015,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="171" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="171" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A171" s="18" t="s">
         <v>662</v>
       </c>
@@ -13389,7 +13044,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="172" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="172" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A172" s="18" t="s">
         <v>666</v>
       </c>
@@ -13418,7 +13073,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="1:9">
+    <row r="173" hidden="1" customHeight="1" spans="1:9">
       <c r="A173" s="4" t="s">
         <v>670</v>
       </c>
@@ -13505,7 +13160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" customHeight="1" spans="1:9">
+    <row r="176" hidden="1" customHeight="1" spans="1:9">
       <c r="A176" s="4" t="s">
         <v>681</v>
       </c>
@@ -13563,7 +13218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" customHeight="1" spans="1:9">
+    <row r="178" hidden="1" customHeight="1" spans="1:9">
       <c r="A178" s="4" t="s">
         <v>689</v>
       </c>
@@ -13621,7 +13276,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="180" customHeight="1" spans="1:9">
+    <row r="180" hidden="1" customHeight="1" spans="1:9">
       <c r="A180" s="4" t="s">
         <v>695</v>
       </c>
@@ -13650,7 +13305,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" customHeight="1" spans="1:9">
+    <row r="181" hidden="1" customHeight="1" spans="1:9">
       <c r="A181" s="4" t="s">
         <v>696</v>
       </c>
@@ -13679,7 +13334,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="182" customHeight="1" spans="1:9">
+    <row r="182" hidden="1" customHeight="1" spans="1:9">
       <c r="A182" s="4" t="s">
         <v>698</v>
       </c>
@@ -13708,7 +13363,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" customHeight="1" spans="1:9">
+    <row r="183" hidden="1" customHeight="1" spans="1:9">
       <c r="A183" s="4" t="s">
         <v>702</v>
       </c>
@@ -13737,7 +13392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="184" customHeight="1" spans="1:9">
+    <row r="184" hidden="1" customHeight="1" spans="1:9">
       <c r="A184" s="31" t="s">
         <v>705</v>
       </c>
@@ -13766,7 +13421,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" customHeight="1" spans="1:9">
+    <row r="185" hidden="1" customHeight="1" spans="1:9">
       <c r="A185" s="4" t="s">
         <v>708</v>
       </c>
@@ -13795,7 +13450,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="1:9">
+    <row r="186" hidden="1" customHeight="1" spans="1:9">
       <c r="A186" s="4" t="s">
         <v>711</v>
       </c>
@@ -13882,7 +13537,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="189" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A189" s="18" t="s">
         <v>723</v>
       </c>
@@ -13911,7 +13566,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="190" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A190" s="18" t="s">
         <v>727</v>
       </c>
@@ -14027,7 +13682,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" customHeight="1" spans="1:9">
+    <row r="194" hidden="1" customHeight="1" spans="1:9">
       <c r="A194" s="4" t="s">
         <v>743</v>
       </c>
@@ -14056,7 +13711,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" customHeight="1" spans="1:9">
+    <row r="195" hidden="1" customHeight="1" spans="1:9">
       <c r="A195" s="4" t="s">
         <v>747</v>
       </c>
@@ -14085,7 +13740,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" customHeight="1" spans="1:9">
+    <row r="196" hidden="1" customHeight="1" spans="1:9">
       <c r="A196" s="4" t="s">
         <v>751</v>
       </c>
@@ -14143,7 +13798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" customHeight="1" spans="1:9">
+    <row r="198" hidden="1" customHeight="1" spans="1:9">
       <c r="A198" s="4" t="s">
         <v>759</v>
       </c>
@@ -14317,7 +13972,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" customHeight="1" spans="1:9">
+    <row r="204" hidden="1" customHeight="1" spans="1:9">
       <c r="A204" s="4" t="s">
         <v>783</v>
       </c>
@@ -14346,7 +14001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" customHeight="1" spans="1:9">
+    <row r="205" hidden="1" customHeight="1" spans="1:9">
       <c r="A205" s="4" t="s">
         <v>786</v>
       </c>
@@ -14491,7 +14146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" customHeight="1" spans="1:9">
+    <row r="210" hidden="1" customHeight="1" spans="1:9">
       <c r="A210" s="4" t="s">
         <v>806</v>
       </c>
@@ -14520,7 +14175,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="211" customHeight="1" spans="1:9">
+    <row r="211" hidden="1" customHeight="1" spans="1:9">
       <c r="A211" s="4" t="s">
         <v>810</v>
       </c>
@@ -14549,7 +14204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" customHeight="1" spans="1:9">
+    <row r="212" hidden="1" customHeight="1" spans="1:9">
       <c r="A212" s="4" t="s">
         <v>814</v>
       </c>
@@ -14752,7 +14407,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="219" customHeight="1" spans="1:9">
+    <row r="219" hidden="1" customHeight="1" spans="1:9">
       <c r="A219" s="4" t="s">
         <v>842</v>
       </c>
@@ -14865,7 +14520,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="223" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A223" s="18" t="s">
         <v>856</v>
       </c>
@@ -14894,7 +14549,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" customHeight="1" spans="1:9">
+    <row r="224" hidden="1" customHeight="1" spans="1:9">
       <c r="A224" s="4" t="s">
         <v>860</v>
       </c>
@@ -14952,7 +14607,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="226" customHeight="1" spans="1:9">
+    <row r="226" hidden="1" customHeight="1" spans="1:9">
       <c r="A226" s="4" t="s">
         <v>867</v>
       </c>
@@ -14981,7 +14636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" customHeight="1" spans="1:9">
+    <row r="227" hidden="1" customHeight="1" spans="1:9">
       <c r="A227" s="4" t="s">
         <v>871</v>
       </c>
@@ -15039,7 +14694,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" customHeight="1" spans="1:9">
+    <row r="229" hidden="1" customHeight="1" spans="1:9">
       <c r="A229" s="4" t="s">
         <v>879</v>
       </c>
@@ -15068,7 +14723,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="230" customHeight="1" spans="1:9">
+    <row r="230" hidden="1" customHeight="1" spans="1:9">
       <c r="A230" s="4" t="s">
         <v>884</v>
       </c>
@@ -15097,7 +14752,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="231" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="231" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A231" s="18" t="s">
         <v>888</v>
       </c>
@@ -15416,7 +15071,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="242" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="242" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A242" s="18" t="s">
         <v>930</v>
       </c>
@@ -15503,7 +15158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="245" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="245" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A245" s="18" t="s">
         <v>941</v>
       </c>
@@ -15532,7 +15187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" customHeight="1" spans="1:9">
+    <row r="246" hidden="1" customHeight="1" spans="1:9">
       <c r="A246" s="4" t="s">
         <v>945</v>
       </c>
@@ -15648,7 +15303,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" customHeight="1" spans="1:9">
+    <row r="250" hidden="1" customHeight="1" spans="1:9">
       <c r="A250" s="4" t="s">
         <v>961</v>
       </c>
@@ -15677,7 +15332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" customHeight="1" spans="1:9">
+    <row r="251" hidden="1" customHeight="1" spans="1:9">
       <c r="A251" s="4" t="s">
         <v>965</v>
       </c>
@@ -15706,7 +15361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" customHeight="1" spans="1:9">
+    <row r="252" hidden="1" customHeight="1" spans="1:9">
       <c r="A252" s="4" t="s">
         <v>969</v>
       </c>
@@ -15735,7 +15390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" customHeight="1" spans="1:9">
+    <row r="253" hidden="1" customHeight="1" spans="1:9">
       <c r="A253" s="4" t="s">
         <v>972</v>
       </c>
@@ -15793,7 +15448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" customHeight="1" spans="1:9">
+    <row r="255" hidden="1" customHeight="1" spans="1:9">
       <c r="A255" s="4" t="s">
         <v>980</v>
       </c>
@@ -15822,7 +15477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" customHeight="1" spans="1:9">
+    <row r="256" hidden="1" customHeight="1" spans="1:9">
       <c r="A256" s="4" t="s">
         <v>984</v>
       </c>
@@ -15851,7 +15506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" customHeight="1" spans="1:9">
+    <row r="257" hidden="1" customHeight="1" spans="1:9">
       <c r="A257" s="4" t="s">
         <v>987</v>
       </c>
@@ -15880,7 +15535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" customHeight="1" spans="1:9">
+    <row r="258" hidden="1" customHeight="1" spans="1:9">
       <c r="A258" s="4" t="s">
         <v>991</v>
       </c>
@@ -15996,7 +15651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="262" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A262" s="2" t="s">
         <v>1006</v>
       </c>
@@ -16025,7 +15680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" customHeight="1" spans="1:9">
+    <row r="263" hidden="1" customHeight="1" spans="1:9">
       <c r="A263" s="4" t="s">
         <v>1010</v>
       </c>
@@ -16054,7 +15709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="264" customHeight="1" spans="1:9">
+    <row r="264" hidden="1" customHeight="1" spans="1:9">
       <c r="A264" s="4" t="s">
         <v>1013</v>
       </c>
@@ -16083,7 +15738,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="265" customHeight="1" spans="1:9">
+    <row r="265" hidden="1" customHeight="1" spans="1:9">
       <c r="A265" s="4" t="s">
         <v>1017</v>
       </c>
@@ -16112,7 +15767,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="266" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A266" s="2" t="s">
         <v>1021</v>
       </c>
@@ -16141,7 +15796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" customHeight="1" spans="1:9">
+    <row r="267" hidden="1" customHeight="1" spans="1:9">
       <c r="A267" s="4" t="s">
         <v>1025</v>
       </c>
@@ -16170,7 +15825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" customHeight="1" spans="1:9">
+    <row r="268" hidden="1" customHeight="1" spans="1:9">
       <c r="A268" s="4" t="s">
         <v>1028</v>
       </c>
@@ -16257,7 +15912,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="271" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="271" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A271" s="18" t="s">
         <v>1039</v>
       </c>
@@ -16315,7 +15970,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="273" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="273" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A273" s="2" t="s">
         <v>1047</v>
       </c>
@@ -16344,7 +15999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" customHeight="1" spans="1:9">
+    <row r="274" hidden="1" customHeight="1" spans="1:9">
       <c r="A274" s="4" t="s">
         <v>1051</v>
       </c>
@@ -16402,7 +16057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" customHeight="1" spans="1:9">
+    <row r="276" hidden="1" customHeight="1" spans="1:9">
       <c r="A276" s="4" t="s">
         <v>1059</v>
       </c>
@@ -16431,7 +16086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" customHeight="1" spans="1:9">
+    <row r="277" hidden="1" customHeight="1" spans="1:9">
       <c r="A277" s="4" t="s">
         <v>1064</v>
       </c>
@@ -16547,7 +16202,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="281" customHeight="1" spans="1:9">
+    <row r="281" hidden="1" customHeight="1" spans="1:9">
       <c r="A281" s="4" t="s">
         <v>1079</v>
       </c>
@@ -16576,7 +16231,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="282" s="22" customFormat="1" customHeight="1" spans="1:9">
+    <row r="282" s="22" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A282" s="22" t="s">
         <v>1083</v>
       </c>
@@ -16605,7 +16260,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="283" customHeight="1" spans="1:9">
+    <row r="283" hidden="1" customHeight="1" spans="1:9">
       <c r="A283" s="4" t="s">
         <v>1087</v>
       </c>
@@ -16634,7 +16289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="284" customHeight="1" spans="1:9">
+    <row r="284" hidden="1" customHeight="1" spans="1:9">
       <c r="A284" s="4" t="s">
         <v>1091</v>
       </c>
@@ -16692,7 +16347,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="286" customHeight="1" spans="1:9">
+    <row r="286" hidden="1" customHeight="1" spans="1:9">
       <c r="A286" s="4" t="s">
         <v>1098</v>
       </c>
@@ -16750,7 +16405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" customHeight="1" spans="1:9">
+    <row r="288" hidden="1" customHeight="1" spans="1:9">
       <c r="A288" s="4" t="s">
         <v>1106</v>
       </c>
@@ -16779,7 +16434,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="289" customHeight="1" spans="1:9">
+    <row r="289" hidden="1" customHeight="1" spans="1:9">
       <c r="A289" s="4" t="s">
         <v>1110</v>
       </c>
@@ -16808,7 +16463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="290" customHeight="1" spans="1:9">
+    <row r="290" hidden="1" customHeight="1" spans="1:9">
       <c r="A290" s="4" t="s">
         <v>1114</v>
       </c>
@@ -16866,7 +16521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="292" customHeight="1" spans="1:9">
+    <row r="292" hidden="1" customHeight="1" spans="1:9">
       <c r="A292" s="4" t="s">
         <v>1121</v>
       </c>
@@ -16895,7 +16550,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="293" customHeight="1" spans="1:9">
+    <row r="293" hidden="1" customHeight="1" spans="1:9">
       <c r="A293" s="4" t="s">
         <v>1125</v>
       </c>
@@ -16953,7 +16608,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" s="22" customFormat="1" customHeight="1" spans="1:9">
+    <row r="295" s="22" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A295" s="22" t="s">
         <v>1134</v>
       </c>
@@ -16982,7 +16637,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="296" customHeight="1" spans="1:9">
+    <row r="296" hidden="1" customHeight="1" spans="1:9">
       <c r="A296" s="4" t="s">
         <v>1138</v>
       </c>
@@ -17011,7 +16666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" s="22" customFormat="1" customHeight="1" spans="1:9">
+    <row r="297" s="22" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A297" s="22" t="s">
         <v>1142</v>
       </c>
@@ -17040,7 +16695,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="298" customHeight="1" spans="1:9">
+    <row r="298" hidden="1" customHeight="1" spans="1:9">
       <c r="A298" s="4" t="s">
         <v>1145</v>
       </c>
@@ -17127,7 +16782,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="301" customHeight="1" spans="1:9">
+    <row r="301" hidden="1" customHeight="1" spans="1:9">
       <c r="A301" s="4" t="s">
         <v>1157</v>
       </c>
@@ -17156,7 +16811,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="302" s="23" customFormat="1" customHeight="1" spans="1:9">
+    <row r="302" s="23" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A302" s="23" t="s">
         <v>1161</v>
       </c>
@@ -17185,7 +16840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="303" customHeight="1" spans="1:9">
+    <row r="303" hidden="1" customHeight="1" spans="1:9">
       <c r="A303" s="4" t="s">
         <v>1165</v>
       </c>
@@ -17214,7 +16869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="304" customHeight="1" spans="1:9">
+    <row r="304" hidden="1" customHeight="1" spans="1:9">
       <c r="A304" s="4" t="s">
         <v>1168</v>
       </c>
@@ -17243,7 +16898,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="305" customHeight="1" spans="1:9">
+    <row r="305" hidden="1" customHeight="1" spans="1:9">
       <c r="A305" s="4" t="s">
         <v>1172</v>
       </c>
@@ -17272,7 +16927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="306" customHeight="1" spans="1:9">
+    <row r="306" hidden="1" customHeight="1" spans="1:9">
       <c r="A306" s="4" t="s">
         <v>1176</v>
       </c>
@@ -17330,7 +16985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="308" customHeight="1" spans="1:9">
+    <row r="308" hidden="1" customHeight="1" spans="1:9">
       <c r="A308" s="4" t="s">
         <v>1184</v>
       </c>
@@ -17359,7 +17014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="309" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="309" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A309" s="18" t="s">
         <v>1188</v>
       </c>
@@ -17388,7 +17043,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="310" customHeight="1" spans="1:9">
+    <row r="310" hidden="1" customHeight="1" spans="1:9">
       <c r="A310" s="4" t="s">
         <v>1192</v>
       </c>
@@ -17475,7 +17130,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="313" customHeight="1" spans="1:9">
+    <row r="313" hidden="1" customHeight="1" spans="1:9">
       <c r="A313" s="4" t="s">
         <v>1204</v>
       </c>
@@ -17562,7 +17217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="316" customHeight="1" spans="1:9">
+    <row r="316" hidden="1" customHeight="1" spans="1:9">
       <c r="A316" s="4" t="s">
         <v>1215</v>
       </c>
@@ -17620,7 +17275,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="318" customHeight="1" spans="1:9">
+    <row r="318" hidden="1" customHeight="1" spans="1:9">
       <c r="A318" s="4" t="s">
         <v>1223</v>
       </c>
@@ -17678,7 +17333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="320" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="320" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A320" s="2" t="s">
         <v>1231</v>
       </c>
@@ -17707,7 +17362,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="321" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="321" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A321" s="2" t="s">
         <v>1235</v>
       </c>
@@ -17736,7 +17391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="322" customHeight="1" spans="1:9">
+    <row r="322" hidden="1" customHeight="1" spans="1:9">
       <c r="A322" s="4" t="s">
         <v>1239</v>
       </c>
@@ -17765,7 +17420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="323" customHeight="1" spans="1:9">
+    <row r="323" hidden="1" customHeight="1" spans="1:9">
       <c r="A323" s="4" t="s">
         <v>1243</v>
       </c>
@@ -17881,7 +17536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="327" customHeight="1" spans="1:9">
+    <row r="327" hidden="1" customHeight="1" spans="1:9">
       <c r="A327" s="4" t="s">
         <v>1258</v>
       </c>
@@ -17910,7 +17565,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="328" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="328" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A328" s="18" t="s">
         <v>1261</v>
       </c>
@@ -17939,7 +17594,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="329" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="329" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A329" s="18" t="s">
         <v>1264</v>
       </c>
@@ -18055,7 +17710,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="333" customHeight="1" spans="1:9">
+    <row r="333" hidden="1" customHeight="1" spans="1:9">
       <c r="A333" s="4" t="s">
         <v>1281</v>
       </c>
@@ -18084,7 +17739,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="334" customHeight="1" spans="1:9">
+    <row r="334" hidden="1" customHeight="1" spans="1:9">
       <c r="A334" s="4" t="s">
         <v>1284</v>
       </c>
@@ -18142,7 +17797,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="336" customHeight="1" spans="1:9">
+    <row r="336" hidden="1" customHeight="1" spans="1:9">
       <c r="A336" s="4" t="s">
         <v>1291</v>
       </c>
@@ -18171,7 +17826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="337" customHeight="1" spans="1:9">
+    <row r="337" hidden="1" customHeight="1" spans="1:9">
       <c r="A337" s="4" t="s">
         <v>1295</v>
       </c>
@@ -18200,7 +17855,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="338" customHeight="1" spans="1:9">
+    <row r="338" hidden="1" customHeight="1" spans="1:9">
       <c r="A338" s="4" t="s">
         <v>1298</v>
       </c>
@@ -18258,7 +17913,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="340" customHeight="1" spans="1:9">
+    <row r="340" hidden="1" customHeight="1" spans="1:9">
       <c r="A340" s="4" t="s">
         <v>1306</v>
       </c>
@@ -18287,7 +17942,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="341" customHeight="1" spans="1:9">
+    <row r="341" hidden="1" customHeight="1" spans="1:9">
       <c r="A341" s="4" t="s">
         <v>1309</v>
       </c>
@@ -18345,7 +18000,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="343" customHeight="1" spans="1:9">
+    <row r="343" hidden="1" customHeight="1" spans="1:9">
       <c r="A343" s="4" t="s">
         <v>1317</v>
       </c>
@@ -18403,7 +18058,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="345" customHeight="1" spans="1:9">
+    <row r="345" hidden="1" customHeight="1" spans="1:9">
       <c r="A345" s="4" t="s">
         <v>1325</v>
       </c>
@@ -18432,7 +18087,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="346" customHeight="1" spans="1:9">
+    <row r="346" hidden="1" customHeight="1" spans="1:9">
       <c r="A346" s="4" t="s">
         <v>1328</v>
       </c>
@@ -18461,7 +18116,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="347" customHeight="1" spans="1:9">
+    <row r="347" hidden="1" customHeight="1" spans="1:9">
       <c r="A347" s="4" t="s">
         <v>1332</v>
       </c>
@@ -18490,7 +18145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="348" customHeight="1" spans="1:9">
+    <row r="348" hidden="1" customHeight="1" spans="1:9">
       <c r="A348" s="4" t="s">
         <v>1336</v>
       </c>
@@ -18519,7 +18174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="349" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="349" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A349" s="18" t="s">
         <v>1339</v>
       </c>
@@ -18548,7 +18203,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="350" customHeight="1" spans="1:9">
+    <row r="350" hidden="1" customHeight="1" spans="1:9">
       <c r="A350" s="4" t="s">
         <v>1343</v>
       </c>
@@ -18577,7 +18232,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="351" customHeight="1" spans="1:9">
+    <row r="351" hidden="1" customHeight="1" spans="1:9">
       <c r="A351" s="4" t="s">
         <v>1347</v>
       </c>
@@ -18606,7 +18261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="352" customHeight="1" spans="1:9">
+    <row r="352" hidden="1" customHeight="1" spans="1:9">
       <c r="A352" s="4" t="s">
         <v>1351</v>
       </c>
@@ -18635,7 +18290,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="353" customHeight="1" spans="1:9">
+    <row r="353" hidden="1" customHeight="1" spans="1:9">
       <c r="A353" s="4" t="s">
         <v>1354</v>
       </c>
@@ -18693,7 +18348,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="355" customHeight="1" spans="1:9">
+    <row r="355" hidden="1" customHeight="1" spans="1:9">
       <c r="A355" s="4" t="s">
         <v>1358</v>
       </c>
@@ -18722,7 +18377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="356" customHeight="1" spans="1:9">
+    <row r="356" hidden="1" customHeight="1" spans="1:9">
       <c r="A356" s="4" t="s">
         <v>1362</v>
       </c>
@@ -18780,7 +18435,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="358" customHeight="1" spans="1:9">
+    <row r="358" hidden="1" customHeight="1" spans="1:9">
       <c r="A358" s="4" t="s">
         <v>1368</v>
       </c>
@@ -18867,7 +18522,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="361" customHeight="1" spans="1:9">
+    <row r="361" hidden="1" customHeight="1" spans="1:9">
       <c r="A361" s="4" t="s">
         <v>1379</v>
       </c>
@@ -18896,7 +18551,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="362" customHeight="1" spans="1:9">
+    <row r="362" hidden="1" customHeight="1" spans="1:9">
       <c r="A362" s="4" t="s">
         <v>1383</v>
       </c>
@@ -18925,7 +18580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="363" customHeight="1" spans="1:9">
+    <row r="363" hidden="1" customHeight="1" spans="1:9">
       <c r="A363" s="4" t="s">
         <v>1387</v>
       </c>
@@ -18954,7 +18609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="364" customHeight="1" spans="1:9">
+    <row r="364" hidden="1" customHeight="1" spans="1:9">
       <c r="A364" s="4" t="s">
         <v>1390</v>
       </c>
@@ -19070,7 +18725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="368" customHeight="1" spans="1:9">
+    <row r="368" hidden="1" customHeight="1" spans="1:9">
       <c r="A368" s="4" t="s">
         <v>1404</v>
       </c>
@@ -19099,7 +18754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="369" customHeight="1" spans="1:9">
+    <row r="369" hidden="1" customHeight="1" spans="1:9">
       <c r="A369" s="4" t="s">
         <v>1408</v>
       </c>
@@ -19157,7 +18812,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="371" customHeight="1" spans="1:9">
+    <row r="371" hidden="1" customHeight="1" spans="1:9">
       <c r="A371" s="4" t="s">
         <v>1416</v>
       </c>
@@ -19186,7 +18841,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="372" customHeight="1" spans="1:9">
+    <row r="372" hidden="1" customHeight="1" spans="1:9">
       <c r="A372" s="4" t="s">
         <v>1420</v>
       </c>
@@ -19244,7 +18899,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="374" customHeight="1" spans="1:9">
+    <row r="374" hidden="1" customHeight="1" spans="1:9">
       <c r="A374" s="4" t="s">
         <v>1427</v>
       </c>
@@ -19302,7 +18957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="376" customHeight="1" spans="1:9">
+    <row r="376" hidden="1" customHeight="1" spans="1:9">
       <c r="A376" s="4" t="s">
         <v>1433</v>
       </c>
@@ -19351,7 +19006,7 @@
         <v>128</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>29</v>
+        <v>1440</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>16</v>
@@ -19362,16 +19017,16 @@
     </row>
     <row r="378" customHeight="1" spans="1:9">
       <c r="A378" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="E378" s="4" t="s">
         <v>35</v>
@@ -19389,18 +19044,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="379" customHeight="1" spans="1:9">
+    <row r="379" hidden="1" customHeight="1" spans="1:9">
       <c r="A379" s="4" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="E379" s="4" t="s">
         <v>46</v>
@@ -19418,15 +19073,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="380" customHeight="1" spans="1:9">
+    <row r="380" hidden="1" customHeight="1" spans="1:9">
       <c r="A380" s="4" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>21</v>
@@ -19449,16 +19104,16 @@
     </row>
     <row r="381" customHeight="1" spans="1:9">
       <c r="A381" s="4" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="E381" s="4" t="s">
         <v>35</v>
@@ -19478,16 +19133,16 @@
     </row>
     <row r="382" customHeight="1" spans="1:9">
       <c r="A382" s="4" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B382" s="24" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="E382" s="4" t="s">
         <v>35</v>
@@ -19507,16 +19162,16 @@
     </row>
     <row r="383" customHeight="1" spans="1:9">
       <c r="A383" s="4" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="E383" s="4" t="s">
         <v>35</v>
@@ -19536,16 +19191,16 @@
     </row>
     <row r="384" customHeight="1" spans="1:9">
       <c r="A384" s="4" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>1414</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="E384" s="4" t="s">
         <v>13</v>
@@ -19565,16 +19220,16 @@
     </row>
     <row r="385" customHeight="1" spans="1:9">
       <c r="A385" s="4" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E385" s="4" t="s">
         <v>35</v>
@@ -19592,15 +19247,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="386" customHeight="1" spans="1:9">
+    <row r="386" hidden="1" customHeight="1" spans="1:9">
       <c r="A386" s="4" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>21</v>
@@ -19623,16 +19278,16 @@
     </row>
     <row r="387" customHeight="1" spans="1:9">
       <c r="A387" s="4" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="E387" s="4" t="s">
         <v>952</v>
@@ -19652,16 +19307,16 @@
     </row>
     <row r="388" customHeight="1" spans="1:9">
       <c r="A388" s="4" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="E388" s="4" t="s">
         <v>35</v>
@@ -19679,18 +19334,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="389" customHeight="1" spans="1:9">
+    <row r="389" hidden="1" customHeight="1" spans="1:9">
       <c r="A389" s="4" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B389" s="24" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="E389" s="4" t="s">
         <v>13</v>
@@ -19710,16 +19365,16 @@
     </row>
     <row r="390" customHeight="1" spans="1:9">
       <c r="A390" s="4" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E390" s="4" t="s">
         <v>35</v>
@@ -19737,18 +19392,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="391" customHeight="1" spans="1:9">
+    <row r="391" hidden="1" customHeight="1" spans="1:9">
       <c r="A391" s="4" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="E391" s="4" t="s">
         <v>217</v>
@@ -19768,19 +19423,19 @@
     </row>
     <row r="392" customHeight="1" spans="1:9">
       <c r="A392" s="4" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="E392" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="F392" s="4" t="s">
         <v>61</v>
@@ -19797,16 +19452,16 @@
     </row>
     <row r="393" customHeight="1" spans="1:9">
       <c r="A393" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="E393" s="4" t="s">
         <v>13</v>
@@ -19824,18 +19479,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="394" s="18" customFormat="1" customHeight="1" spans="1:9">
+    <row r="394" s="18" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A394" s="18" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B394" s="18" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C394" s="18" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="D394" s="18" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="E394" s="18" t="s">
         <v>13</v>
@@ -19855,16 +19510,16 @@
     </row>
     <row r="395" customHeight="1" spans="1:9">
       <c r="A395" s="4" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B395" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D395" s="4" t="s">
         <v>1506</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>1507</v>
-      </c>
-      <c r="D395" s="4" t="s">
-        <v>1505</v>
       </c>
       <c r="E395" s="4" t="s">
         <v>35</v>
@@ -19882,18 +19537,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="396" customHeight="1" spans="1:9">
+    <row r="396" hidden="1" customHeight="1" spans="1:9">
       <c r="A396" s="4" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B396" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D396" s="4" t="s">
         <v>1509</v>
-      </c>
-      <c r="C396" s="4" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D396" s="4" t="s">
-        <v>1508</v>
       </c>
       <c r="E396" s="4" t="s">
         <v>35</v>
@@ -19911,18 +19566,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="397" customHeight="1" spans="1:9">
+    <row r="397" hidden="1" customHeight="1" spans="1:9">
       <c r="A397" s="4" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="E397" s="4" t="s">
         <v>35</v>
@@ -19940,18 +19595,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="398" customHeight="1" spans="1:9">
+    <row r="398" hidden="1" customHeight="1" spans="1:9">
       <c r="A398" s="4" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="E398" s="4" t="s">
         <v>35</v>
@@ -19969,18 +19624,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="399" customHeight="1" spans="1:9">
+    <row r="399" hidden="1" customHeight="1" spans="1:9">
       <c r="A399" s="4" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="E399" s="4" t="s">
         <v>35</v>
@@ -19998,18 +19653,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="400" customHeight="1" spans="1:9">
+    <row r="400" hidden="1" customHeight="1" spans="1:9">
       <c r="A400" s="4" t="s">
         <v>470</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>1402</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="E400" s="4" t="s">
         <v>13</v>
@@ -20029,13 +19684,13 @@
     </row>
     <row r="401" customHeight="1" spans="1:9">
       <c r="A401" s="4" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>1324</v>
@@ -20058,13 +19713,13 @@
     </row>
     <row r="402" customHeight="1" spans="1:9">
       <c r="A402" s="4" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B402" s="24" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>528</v>
@@ -20087,16 +19742,16 @@
     </row>
     <row r="403" customHeight="1" spans="1:9">
       <c r="A403" s="4" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="E403" s="4" t="s">
         <v>46</v>
@@ -20116,13 +19771,13 @@
     </row>
     <row r="404" customHeight="1" spans="1:9">
       <c r="A404" s="4" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>21</v>
@@ -20143,18 +19798,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="405" customHeight="1" spans="1:9">
+    <row r="405" hidden="1" customHeight="1" spans="1:9">
       <c r="A405" s="4" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B405" s="24" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D405" s="4" t="s">
         <v>1538</v>
-      </c>
-      <c r="C405" s="4" t="s">
-        <v>1539</v>
-      </c>
-      <c r="D405" s="4" t="s">
-        <v>1537</v>
       </c>
       <c r="E405" s="4" t="s">
         <v>35</v>
@@ -20172,18 +19827,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="406" customHeight="1" spans="1:9">
+    <row r="406" hidden="1" customHeight="1" spans="1:9">
       <c r="A406" s="4" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B406" s="24" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="E406" s="4" t="s">
         <v>46</v>
@@ -20201,18 +19856,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="407" customHeight="1" spans="1:9">
+    <row r="407" hidden="1" customHeight="1" spans="1:9">
       <c r="A407" s="4" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="E407" s="4" t="s">
         <v>13</v>
@@ -20230,18 +19885,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="408" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="408" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A408" s="2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="C408" s="33" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="D408" s="34" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>13</v>
@@ -20261,16 +19916,16 @@
     </row>
     <row r="409" s="2" customFormat="1" customHeight="1" spans="1:9">
       <c r="A409" s="2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B409" s="26" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>46</v>
@@ -20290,16 +19945,16 @@
     </row>
     <row r="410" customHeight="1" spans="1:9">
       <c r="A410" s="4" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>1414</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="E410" s="4" t="s">
         <v>35</v>
@@ -20319,16 +19974,16 @@
     </row>
     <row r="411" customHeight="1" spans="1:9">
       <c r="A411" s="4" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="E411" s="4" t="s">
         <v>35</v>
@@ -20348,13 +20003,13 @@
     </row>
     <row r="412" customHeight="1" spans="1:9">
       <c r="A412" s="4" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>21</v>
@@ -20377,16 +20032,16 @@
     </row>
     <row r="413" customHeight="1" spans="1:9">
       <c r="A413" s="4" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="E413" s="4" t="s">
         <v>46</v>
@@ -20404,18 +20059,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="414" customHeight="1" spans="1:9">
+    <row r="414" hidden="1" customHeight="1" spans="1:9">
       <c r="A414" s="4" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="E414" s="4" t="s">
         <v>35</v>
@@ -20433,18 +20088,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="415" customHeight="1" spans="1:9">
+    <row r="415" hidden="1" customHeight="1" spans="1:9">
       <c r="A415" s="4" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="E415" s="4" t="s">
         <v>35</v>
@@ -20464,13 +20119,13 @@
     </row>
     <row r="416" customHeight="1" spans="1:9">
       <c r="A416" s="4" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>1433</v>
@@ -20491,18 +20146,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="417" customHeight="1" spans="1:9">
+    <row r="417" hidden="1" customHeight="1" spans="1:9">
       <c r="A417" s="4" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="E417" s="4" t="s">
         <v>13</v>
@@ -20520,15 +20175,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="418" customHeight="1" spans="1:9">
+    <row r="418" hidden="1" customHeight="1" spans="1:9">
       <c r="A418" s="4" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>528</v>
@@ -20549,18 +20204,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="419" customHeight="1" spans="1:9">
+    <row r="419" hidden="1" customHeight="1" spans="1:9">
       <c r="A419" s="4" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E419" s="4" t="s">
         <v>13</v>
@@ -20578,18 +20233,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="420" customHeight="1" spans="1:9">
+    <row r="420" hidden="1" customHeight="1" spans="1:9">
       <c r="A420" s="4" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="E420" s="4" t="s">
         <v>13</v>
@@ -20607,18 +20262,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="421" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="421" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A421" s="2" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>46</v>
@@ -20636,15 +20291,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="422" customHeight="1" spans="1:9">
+    <row r="422" hidden="1" customHeight="1" spans="1:9">
       <c r="A422" s="4" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>21</v>
@@ -20665,18 +20320,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="423" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="423" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A423" s="2" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>263</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>35</v>
@@ -20696,16 +20351,16 @@
     </row>
     <row r="424" ht="13.85" spans="1:9">
       <c r="A424" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B424" s="24" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="E424" s="4" t="s">
         <v>13</v>
@@ -20723,18 +20378,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="425" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="425" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A425" s="2" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>13</v>
@@ -20754,13 +20409,13 @@
     </row>
     <row r="426" s="2" customFormat="1" customHeight="1" spans="1:9">
       <c r="A426" s="2" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B426" s="26" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" s="2" t="s">
@@ -20779,15 +20434,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="427" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="427" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A427" s="2" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" s="2" t="s">
@@ -20806,15 +20461,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="428" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="428" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:9">
       <c r="A428" s="4" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4" t="s">
@@ -20833,9 +20488,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="429" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="429" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A429" s="4" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B429" s="4" t="s">
         <v>219</v>
@@ -20864,16 +20519,16 @@
     </row>
     <row r="430" s="2" customFormat="1" ht="13.85" spans="1:9">
       <c r="A430" s="4" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="E430" s="4" t="s">
         <v>13</v>
@@ -20891,18 +20546,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="431" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="431" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A431" s="4" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B431" s="4" t="s">
         <v>1169</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="E431" s="4" t="s">
         <v>27</v>
@@ -20922,16 +20577,16 @@
     </row>
     <row r="432" s="2" customFormat="1" ht="13.85" spans="1:9">
       <c r="A432" s="4" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="E432" s="4" t="s">
         <v>822</v>
@@ -20951,16 +20606,16 @@
     </row>
     <row r="433" s="2" customFormat="1" ht="13.85" spans="1:9">
       <c r="A433" s="4" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B433" s="4" t="s">
         <v>820</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="E433" s="4" t="s">
         <v>822</v>
@@ -20978,18 +20633,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="434" s="2" customFormat="1" ht="15.75" spans="1:9">
+    <row r="434" s="2" customFormat="1" ht="15.75" hidden="1" spans="1:9">
       <c r="A434" s="4" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="E434" s="4" t="s">
         <v>13</v>
@@ -21007,18 +20662,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="435" s="2" customFormat="1" ht="13.9" spans="1:9">
+    <row r="435" s="2" customFormat="1" ht="13.9" hidden="1" spans="1:9">
       <c r="A435" s="4" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="E435" s="4" t="s">
         <v>13</v>
@@ -21036,18 +20691,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="436" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="436" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A436" s="4" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="E436" s="4" t="s">
         <v>13</v>
@@ -21065,18 +20720,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="437" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="437" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A437" s="4" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="E437" s="4" t="s">
         <v>13</v>
@@ -21094,18 +20749,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="438" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="438" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A438" s="4" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="E438" s="4" t="s">
         <v>13</v>
@@ -21123,18 +20778,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="439" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="439" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A439" s="4" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D439" s="4" t="s">
         <v>1651</v>
-      </c>
-      <c r="B439" s="4" t="s">
-        <v>1652</v>
-      </c>
-      <c r="C439" s="4" t="s">
-        <v>1653</v>
-      </c>
-      <c r="D439" s="4" t="s">
-        <v>1650</v>
       </c>
       <c r="E439" s="4" t="s">
         <v>13</v>
@@ -21152,18 +20807,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="440" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="440" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A440" s="4" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="E440" s="4" t="s">
         <v>13</v>
@@ -21181,18 +20836,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="441" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="441" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A441" s="4" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="E441" s="4" t="s">
         <v>13</v>
@@ -21210,18 +20865,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="442" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="442" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A442" s="4" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="E442" s="4" t="s">
         <v>13</v>
@@ -21239,18 +20894,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="443" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="443" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A443" s="4" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="E443" s="4" t="s">
         <v>13</v>
@@ -21268,18 +20923,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="444" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="444" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A444" s="4" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E444" s="4" t="s">
         <v>13</v>
@@ -21297,18 +20952,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="445" s="2" customFormat="1" ht="13.9" spans="1:9">
+    <row r="445" s="2" customFormat="1" ht="13.9" hidden="1" spans="1:9">
       <c r="A445" s="4" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="E445" s="4" t="s">
         <v>13</v>
@@ -21326,18 +20981,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="446" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="446" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A446" s="4" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D446" s="4" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="E446" s="4" t="s">
         <v>13</v>
@@ -21355,18 +21010,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="447" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="447" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A447" s="4" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="D447" s="4" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E447" s="4" t="s">
         <v>13</v>
@@ -21384,15 +21039,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="448" s="2" customFormat="1" ht="15.75" spans="1:9">
+    <row r="448" s="2" customFormat="1" ht="15.75" hidden="1" spans="1:9">
       <c r="A448" s="4" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4" t="s">
@@ -21411,15 +21066,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="449" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="449" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A449" s="4" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>1324</v>
@@ -21440,18 +21095,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="450" s="2" customFormat="1" ht="13.9" spans="1:9">
+    <row r="450" s="2" customFormat="1" ht="13.9" hidden="1" spans="1:9">
       <c r="A450" s="4" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="D450" s="4" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="E450" s="4" t="s">
         <v>13</v>
@@ -21469,18 +21124,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="451" s="2" customFormat="1" ht="13.9" spans="1:9">
+    <row r="451" s="2" customFormat="1" ht="13.9" hidden="1" spans="1:9">
       <c r="A451" s="4" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>263</v>
       </c>
       <c r="D451" s="4" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="E451" s="4" t="s">
         <v>13</v>
@@ -21498,12 +21153,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="452" s="2" customFormat="1" ht="13.85" spans="1:9">
+    <row r="452" s="2" customFormat="1" ht="13.85" hidden="1" spans="1:9">
       <c r="A452" s="35" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B452" s="35" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>263</v>
@@ -21525,18 +21180,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="453" s="2" customFormat="1" ht="13.9" spans="1:9">
+    <row r="453" s="2" customFormat="1" ht="13.9" hidden="1" spans="1:9">
       <c r="A453" s="3" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B453" s="37" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="C453" s="37" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="D453" s="37" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E453" s="37" t="s">
         <v>13</v>
@@ -21554,18 +21209,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="454" s="3" customFormat="1" ht="15.85" customHeight="1" spans="1:9">
+    <row r="454" s="3" customFormat="1" ht="15.85" hidden="1" customHeight="1" spans="1:9">
       <c r="A454" s="3" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B454" s="37" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="C454" s="37" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="D454" s="37" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="E454" s="37" t="s">
         <v>13</v>
@@ -21583,18 +21238,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="455" customHeight="1" spans="1:9">
+    <row r="455" hidden="1" customHeight="1" spans="1:9">
       <c r="A455" s="37" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B455" s="37" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="C455" s="37" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D455" s="37" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E455" s="37" t="s">
         <v>13</v>
@@ -21614,16 +21269,16 @@
     </row>
     <row r="456" customHeight="1" spans="1:9">
       <c r="A456" s="37" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B456" s="37" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="C456" s="37" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D456" s="37" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="E456" s="37" t="s">
         <v>13</v>
@@ -21643,16 +21298,16 @@
     </row>
     <row r="457" customHeight="1" spans="1:9">
       <c r="A457" s="37" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B457" s="37" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="C457" s="37" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="D457" s="37" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="E457" s="37" t="s">
         <v>13</v>
@@ -21672,16 +21327,16 @@
     </row>
     <row r="458" customHeight="1" spans="1:9">
       <c r="A458" s="37" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B458" s="37" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="C458" s="37" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D458" s="37" t="s">
         <v>1711</v>
-      </c>
-      <c r="D458" s="37" t="s">
-        <v>1710</v>
       </c>
       <c r="E458" s="37" t="s">
         <v>46</v>
@@ -21699,18 +21354,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="459" customHeight="1" spans="1:9">
+    <row r="459" hidden="1" customHeight="1" spans="1:9">
       <c r="A459" s="37" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B459" s="37" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C459" s="37" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="D459" s="37" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="E459" s="37" t="s">
         <v>13</v>
@@ -21728,18 +21383,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="460" customHeight="1" spans="1:9">
+    <row r="460" hidden="1" customHeight="1" spans="1:9">
       <c r="A460" s="37" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B460" s="37" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="C460" s="37" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="D460" s="37" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="E460" s="37" t="s">
         <v>13</v>
@@ -21757,24 +21412,24 @@
         <v>56</v>
       </c>
     </row>
-    <row r="461" customHeight="1" spans="1:9">
+    <row r="461" hidden="1" customHeight="1" spans="1:9">
       <c r="A461" s="37" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B461" s="37" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="C461" s="37" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D461" s="37" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="E461" s="37" t="s">
         <v>13</v>
       </c>
       <c r="F461" s="37" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>15</v>
@@ -21786,18 +21441,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="462" customHeight="1" spans="1:9">
+    <row r="462" hidden="1" customHeight="1" spans="1:9">
       <c r="A462" s="4" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="C462" s="31" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E462" s="4" t="s">
         <v>13</v>
@@ -21817,19 +21472,24 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I462" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="付费"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <sortState ref="A2:R446">
     <sortCondition ref="A2:A446"/>
   </sortState>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H420 H421:H434 H477:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H434 H477:H1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H435:H462">
       <formula1>"是,否,无法确认"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I420 I421:I462 I477:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I462 I477:I1048576">
       <formula1>"停止更新,持续更新,更新不详"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21883,45 +21543,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:I208"/>
   <sheetFormatPr defaultColWidth="8.46902654867257" defaultRowHeight="13.85"/>
   <cols>
     <col min="1" max="2" width="14.7964601769912" style="4" customWidth="1"/>
     <col min="3" max="3" width="46.7964601769912" style="4" customWidth="1"/>
     <col min="4" max="4" width="33.8141592920354" style="4" customWidth="1"/>
     <col min="5" max="5" width="40.212389380531" style="5" customWidth="1"/>
-    <col min="6" max="6" width="20.5752212389381" style="4" customWidth="1"/>
-    <col min="7" max="7" width="30.1327433628319" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="8.46902654867257" style="4"/>
+    <col min="6" max="16384" width="8.46902654867257" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1734</v>
-      </c>
-      <c r="G1" s="4" t="s">
         <v>1735</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -21932,30 +21584,24 @@
         <v>528</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>1737</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>1738</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>1739</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>528</v>
@@ -21966,14 +21612,8 @@
       <c r="F3" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
@@ -21981,7 +21621,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1743</v>
+        <v>1739</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>528</v>
@@ -21992,14 +21632,8 @@
       <c r="F4" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
@@ -22010,7 +21644,7 @@
         <v>528</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1744</v>
+        <v>1740</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>528</v>
@@ -22018,14 +21652,8 @@
       <c r="F5" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -22036,7 +21664,7 @@
         <v>528</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1745</v>
+        <v>1741</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>528</v>
@@ -22044,14 +21672,8 @@
       <c r="F6" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
@@ -22062,7 +21684,7 @@
         <v>528</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1746</v>
+        <v>1742</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>528</v>
@@ -22070,14 +21692,8 @@
       <c r="F7" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
@@ -22085,7 +21701,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>528</v>
@@ -22096,14 +21712,8 @@
       <c r="F8" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -22111,7 +21721,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1748</v>
+        <v>1744</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>528</v>
@@ -22122,14 +21732,8 @@
       <c r="F9" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
@@ -22137,7 +21741,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1749</v>
+        <v>1745</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>528</v>
@@ -22148,14 +21752,8 @@
       <c r="F10" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
@@ -22174,14 +21772,8 @@
       <c r="F11" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
@@ -22192,7 +21784,7 @@
         <v>528</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>528</v>
@@ -22200,14 +21792,8 @@
       <c r="F12" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
@@ -22226,14 +21812,8 @@
       <c r="F13" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -22252,25 +21832,19 @@
       <c r="F14" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1752</v>
+        <v>1748</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>528</v>
@@ -22278,14 +21852,8 @@
       <c r="F15" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
@@ -22296,7 +21864,7 @@
         <v>528</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1753</v>
+        <v>1749</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>528</v>
@@ -22304,14 +21872,8 @@
       <c r="F16" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -22322,7 +21884,7 @@
         <v>528</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>528</v>
@@ -22330,14 +21892,8 @@
       <c r="F17" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
@@ -22345,7 +21901,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1755</v>
+        <v>1751</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>528</v>
@@ -22356,14 +21912,8 @@
       <c r="F18" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
@@ -22371,7 +21921,7 @@
         <v>56</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>528</v>
@@ -22382,14 +21932,8 @@
       <c r="F19" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
@@ -22397,10 +21941,10 @@
         <v>56</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1757</v>
+        <v>1753</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>528</v>
@@ -22408,14 +21952,8 @@
       <c r="F20" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="4" t="s">
         <v>36</v>
       </c>
@@ -22426,22 +21964,16 @@
         <v>21</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1759</v>
+        <v>1755</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1761</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>1762</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="4" t="s">
         <v>36</v>
       </c>
@@ -22452,22 +21984,16 @@
         <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1764</v>
+        <v>1758</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1765</v>
+        <v>1759</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="4" t="s">
         <v>16</v>
       </c>
@@ -22478,22 +22004,16 @@
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1768</v>
+        <v>1761</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1769</v>
+        <v>1762</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1770</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>1771</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="4" t="s">
         <v>36</v>
       </c>
@@ -22504,22 +22024,16 @@
         <v>21</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1773</v>
+        <v>1764</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1774</v>
+        <v>1765</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1775</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>1776</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:8">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>36</v>
       </c>
@@ -22527,25 +22041,19 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1778</v>
+        <v>1767</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>1779</v>
+        <v>1768</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="4" t="s">
         <v>36</v>
       </c>
@@ -22553,25 +22061,19 @@
         <v>17</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1783</v>
+        <v>1770</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1784</v>
+        <v>1771</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>1785</v>
+        <v>1772</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>1786</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>1787</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>1788</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="4" t="s">
         <v>36</v>
       </c>
@@ -22582,22 +22084,16 @@
         <v>21</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1789</v>
+        <v>1774</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>1791</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -22608,22 +22104,16 @@
         <v>21</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1792</v>
+        <v>1777</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>1794</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="4" t="s">
         <v>36</v>
       </c>
@@ -22634,22 +22124,16 @@
         <v>21</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1796</v>
+        <v>1780</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1797</v>
+        <v>1781</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>1798</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="4" t="s">
         <v>36</v>
       </c>
@@ -22660,22 +22144,16 @@
         <v>21</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1800</v>
+        <v>1783</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>1801</v>
+        <v>1784</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="4" t="s">
         <v>36</v>
       </c>
@@ -22686,22 +22164,16 @@
         <v>21</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1803</v>
+        <v>1786</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>1804</v>
+        <v>1787</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
         <v>16</v>
       </c>
@@ -22712,22 +22184,16 @@
         <v>21</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>1806</v>
+        <v>1789</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>1807</v>
+        <v>1790</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>1808</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>1809</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>1810</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="4" t="s">
         <v>36</v>
       </c>
@@ -22738,22 +22204,16 @@
         <v>21</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1811</v>
+        <v>1792</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>1812</v>
+        <v>1793</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>1813</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="4" t="s">
         <v>36</v>
       </c>
@@ -22764,22 +22224,16 @@
         <v>21</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>1815</v>
+        <v>1795</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>1816</v>
+        <v>1796</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="4" t="s">
         <v>36</v>
       </c>
@@ -22790,22 +22244,16 @@
         <v>21</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1818</v>
+        <v>1798</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1819</v>
+        <v>1799</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>1820</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:8">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:6">
       <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
@@ -22816,22 +22264,16 @@
         <v>21</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1822</v>
+        <v>1801</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1823</v>
+        <v>1802</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:8">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="1:6">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
@@ -22839,25 +22281,19 @@
         <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1827</v>
+        <v>1804</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>1828</v>
+        <v>1805</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:8">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="1:6">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
@@ -22865,25 +22301,19 @@
         <v>17</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1832</v>
+        <v>1807</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1828</v>
+        <v>1805</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:8">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" spans="1:6">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
@@ -22891,25 +22321,19 @@
         <v>17</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1833</v>
+        <v>1808</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>1828</v>
+        <v>1805</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="1:8">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" spans="1:6">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -22917,25 +22341,19 @@
         <v>17</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1834</v>
+        <v>1809</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1828</v>
+        <v>1805</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="1:8">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" spans="1:6">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
@@ -22943,25 +22361,19 @@
         <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1835</v>
+        <v>1810</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>1828</v>
+        <v>1805</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="4" t="s">
         <v>16</v>
       </c>
@@ -22972,22 +22384,16 @@
         <v>21</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>1836</v>
+        <v>1811</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>1837</v>
+        <v>1812</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G42" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="4" t="s">
         <v>16</v>
       </c>
@@ -22998,22 +22404,16 @@
         <v>21</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1838</v>
+        <v>1813</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>1837</v>
+        <v>1812</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G43" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H43" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
@@ -23024,22 +22424,16 @@
         <v>21</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>1839</v>
+        <v>1814</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>1837</v>
+        <v>1812</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G44" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="4" t="s">
         <v>16</v>
       </c>
@@ -23050,22 +22444,16 @@
         <v>21</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>1840</v>
+        <v>1815</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>1837</v>
+        <v>1812</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G45" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="4" t="s">
         <v>16</v>
       </c>
@@ -23076,22 +22464,16 @@
         <v>21</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>1841</v>
+        <v>1816</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>1837</v>
+        <v>1812</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G46" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="4" t="s">
         <v>16</v>
       </c>
@@ -23102,22 +22484,16 @@
         <v>21</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1842</v>
+        <v>1817</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1837</v>
+        <v>1812</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G47" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="4" t="s">
         <v>36</v>
       </c>
@@ -23128,22 +22504,16 @@
         <v>21</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>1843</v>
+        <v>1818</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>1844</v>
+        <v>1819</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>1845</v>
-      </c>
-      <c r="G48" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="4" t="s">
         <v>36</v>
       </c>
@@ -23154,22 +22524,16 @@
         <v>21</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1846</v>
+        <v>1820</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>1844</v>
+        <v>1819</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>1845</v>
-      </c>
-      <c r="G49" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="4" t="s">
         <v>36</v>
       </c>
@@ -23180,22 +22544,16 @@
         <v>21</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>1847</v>
+        <v>1821</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>1848</v>
+        <v>1822</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>1775</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="4" t="s">
         <v>36</v>
       </c>
@@ -23206,22 +22564,16 @@
         <v>21</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1850</v>
+        <v>1824</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>1848</v>
+        <v>1822</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1775</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="4" t="s">
         <v>16</v>
       </c>
@@ -23229,25 +22581,19 @@
         <v>56</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>1851</v>
+        <v>1825</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>528</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>1852</v>
+        <v>1826</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>1853</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="4" t="s">
         <v>16</v>
       </c>
@@ -23255,25 +22601,19 @@
         <v>56</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>1855</v>
+        <v>1828</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>528</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>1856</v>
+        <v>1829</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>1853</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="4" t="s">
         <v>36</v>
       </c>
@@ -23284,22 +22624,16 @@
         <v>21</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>1858</v>
+        <v>1831</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="4" t="s">
         <v>36</v>
       </c>
@@ -23310,22 +22644,16 @@
         <v>21</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>1862</v>
+        <v>1834</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="4" t="s">
         <v>36</v>
       </c>
@@ -23336,22 +22664,16 @@
         <v>21</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>1863</v>
+        <v>1835</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="4" t="s">
         <v>36</v>
       </c>
@@ -23362,22 +22684,16 @@
         <v>21</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1864</v>
+        <v>1836</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="4" t="s">
         <v>36</v>
       </c>
@@ -23388,22 +22704,16 @@
         <v>21</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>1865</v>
+        <v>1837</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="4" t="s">
         <v>36</v>
       </c>
@@ -23414,22 +22724,16 @@
         <v>21</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1866</v>
+        <v>1838</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="4" t="s">
         <v>36</v>
       </c>
@@ -23440,22 +22744,16 @@
         <v>21</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>1867</v>
+        <v>1839</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G60" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H60" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="4" t="s">
         <v>36</v>
       </c>
@@ -23466,22 +22764,16 @@
         <v>21</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1870</v>
+        <v>1841</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G61" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H61" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="4" t="s">
         <v>36</v>
       </c>
@@ -23492,22 +22784,16 @@
         <v>21</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1871</v>
+        <v>1842</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G62" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H62" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="4" t="s">
         <v>36</v>
       </c>
@@ -23518,22 +22804,16 @@
         <v>21</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1872</v>
+        <v>1843</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G63" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H63" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="4" t="s">
         <v>36</v>
       </c>
@@ -23544,22 +22824,16 @@
         <v>21</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1873</v>
+        <v>1844</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G64" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H64" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="4" t="s">
         <v>36</v>
       </c>
@@ -23570,22 +22844,16 @@
         <v>21</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1874</v>
+        <v>1845</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G65" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H65" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="4" t="s">
         <v>36</v>
       </c>
@@ -23596,22 +22864,16 @@
         <v>21</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1875</v>
+        <v>1846</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G66" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="4" t="s">
         <v>36</v>
       </c>
@@ -23622,22 +22884,16 @@
         <v>21</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1876</v>
+        <v>1847</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>1868</v>
+        <v>1840</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G67" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H67" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="4" t="s">
         <v>36</v>
       </c>
@@ -23648,22 +22904,16 @@
         <v>21</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1877</v>
+        <v>1848</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="4" t="s">
         <v>36</v>
       </c>
@@ -23674,22 +22924,16 @@
         <v>21</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1879</v>
+        <v>1850</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="4" t="s">
         <v>36</v>
       </c>
@@ -23700,22 +22944,16 @@
         <v>21</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1880</v>
+        <v>1851</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="4" t="s">
         <v>36</v>
       </c>
@@ -23726,22 +22964,16 @@
         <v>21</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1881</v>
+        <v>1852</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="4" t="s">
         <v>36</v>
       </c>
@@ -23752,22 +22984,16 @@
         <v>21</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1882</v>
+        <v>1853</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="4" t="s">
         <v>36</v>
       </c>
@@ -23778,22 +23004,16 @@
         <v>21</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>1883</v>
+        <v>1854</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="4" t="s">
         <v>36</v>
       </c>
@@ -23804,100 +23024,76 @@
         <v>21</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>1884</v>
+        <v>1855</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" spans="1:8">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="1:6">
       <c r="A75" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1885</v>
+        <v>1856</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>1886</v>
+        <v>1857</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>1887</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" spans="1:8">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:6">
       <c r="A76" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1889</v>
+        <v>1859</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>1886</v>
+        <v>1857</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1887</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="1:8">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:6">
       <c r="A77" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1890</v>
+        <v>1860</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>1886</v>
+        <v>1857</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1887</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="4" t="s">
         <v>16</v>
       </c>
@@ -23905,25 +23101,19 @@
         <v>56</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>1891</v>
+        <v>1861</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>528</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>1892</v>
+        <v>1862</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>1893</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>1894</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="4" t="s">
         <v>16</v>
       </c>
@@ -23934,22 +23124,16 @@
         <v>21</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1896</v>
+        <v>1864</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1897</v>
+        <v>1865</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>1898</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>1899</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="4" t="s">
         <v>36</v>
       </c>
@@ -23957,51 +23141,39 @@
         <v>17</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>1901</v>
+        <v>1867</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>1902</v>
+        <v>1868</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="1:8">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:6">
       <c r="A81" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1904</v>
+        <v>1870</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1905</v>
+        <v>1871</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>1906</v>
+        <v>1872</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1907</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="4" t="s">
         <v>16</v>
       </c>
@@ -24009,25 +23181,19 @@
         <v>56</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>1909</v>
+        <v>1874</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1910</v>
+        <v>1875</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>1911</v>
+        <v>1876</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>1912</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>1913</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="4" t="s">
         <v>36</v>
       </c>
@@ -24038,22 +23204,16 @@
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1915</v>
+        <v>1878</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>1916</v>
+        <v>1879</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="4" t="s">
         <v>36</v>
       </c>
@@ -24061,25 +23221,19 @@
         <v>17</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>1918</v>
+        <v>1881</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>1919</v>
+        <v>1882</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>1920</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="4" t="s">
         <v>16</v>
       </c>
@@ -24087,51 +23241,39 @@
         <v>17</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>1922</v>
+        <v>1884</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>1923</v>
+        <v>1885</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>1920</v>
-      </c>
-      <c r="G85" s="4" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:6">
+      <c r="A86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H85" s="4" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="1:8">
-      <c r="A86" s="1" t="s">
-        <v>1742</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>1925</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>1926</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>1927</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="4" t="s">
         <v>36</v>
       </c>
@@ -24139,25 +23281,19 @@
         <v>17</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>1928</v>
+        <v>1890</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>1929</v>
+        <v>1891</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>1930</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="4" t="s">
         <v>36</v>
       </c>
@@ -24165,25 +23301,19 @@
         <v>17</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>1932</v>
+        <v>1893</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>1933</v>
+        <v>1894</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>1934</v>
-      </c>
-      <c r="H88" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:6">
       <c r="A89" s="4" t="s">
         <v>16</v>
       </c>
@@ -24191,25 +23321,19 @@
         <v>56</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>1935</v>
+        <v>1895</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>1936</v>
+        <v>1896</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>1937</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>1938</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="4" t="s">
         <v>36</v>
       </c>
@@ -24217,25 +23341,19 @@
         <v>17</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>1940</v>
+        <v>1898</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>1941</v>
+        <v>1899</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>1942</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>1943</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="4" t="s">
         <v>36</v>
       </c>
@@ -24243,25 +23361,19 @@
         <v>17</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>1945</v>
+        <v>1901</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>1946</v>
+        <v>1902</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="4" t="s">
         <v>36</v>
       </c>
@@ -24269,25 +23381,19 @@
         <v>17</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>1948</v>
+        <v>1904</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>1946</v>
+        <v>1902</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="4" t="s">
         <v>36</v>
       </c>
@@ -24295,25 +23401,19 @@
         <v>17</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>1949</v>
+        <v>1905</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>1946</v>
+        <v>1902</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="4" t="s">
         <v>36</v>
       </c>
@@ -24321,25 +23421,19 @@
         <v>17</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>1950</v>
+        <v>1906</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>1951</v>
+        <v>1907</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="4" t="s">
         <v>36</v>
       </c>
@@ -24347,25 +23441,19 @@
         <v>17</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>1953</v>
+        <v>1909</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>1954</v>
+        <v>1910</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>1955</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="4" t="s">
         <v>16</v>
       </c>
@@ -24376,22 +23464,16 @@
         <v>21</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>1957</v>
+        <v>1912</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>1958</v>
+        <v>1913</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>1959</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>1960</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="4" t="s">
         <v>16</v>
       </c>
@@ -24399,25 +23481,19 @@
         <v>56</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>1962</v>
+        <v>1915</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>528</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>1963</v>
+        <v>1916</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>1964</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>1965</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="4" t="s">
         <v>36</v>
       </c>
@@ -24428,22 +23504,16 @@
         <v>21</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>1966</v>
+        <v>1918</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>1967</v>
+        <v>1919</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>1968</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="4" t="s">
         <v>36</v>
       </c>
@@ -24454,22 +23524,16 @@
         <v>21</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>1970</v>
+        <v>1921</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>1971</v>
+        <v>1922</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="4" t="s">
         <v>36</v>
       </c>
@@ -24477,25 +23541,19 @@
         <v>17</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>1973</v>
+        <v>1924</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>1974</v>
+        <v>1925</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>1955</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="4" t="s">
         <v>16</v>
       </c>
@@ -24503,25 +23561,19 @@
         <v>56</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>1976</v>
+        <v>1927</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>1977</v>
+        <v>1928</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>1955</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>1978</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="4" t="s">
         <v>16</v>
       </c>
@@ -24529,25 +23581,19 @@
         <v>56</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>1980</v>
+        <v>1930</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>1981</v>
+        <v>1931</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>1982</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="4" t="s">
         <v>16</v>
       </c>
@@ -24555,25 +23601,19 @@
         <v>56</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>1984</v>
+        <v>1933</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>1985</v>
+        <v>1934</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>1986</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>1987</v>
-      </c>
-      <c r="H103" s="4" t="s">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="4" t="s">
         <v>36</v>
       </c>
@@ -24581,25 +23621,19 @@
         <v>17</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>1989</v>
+        <v>1936</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>1990</v>
+        <v>1937</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>1991</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="4" t="s">
         <v>36</v>
       </c>
@@ -24607,25 +23641,19 @@
         <v>17</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>1993</v>
+        <v>1939</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>528</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>1994</v>
+        <v>1940</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>1964</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="4" t="s">
         <v>36</v>
       </c>
@@ -24636,74 +23664,56 @@
         <v>21</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>1996</v>
+        <v>1942</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>1997</v>
+        <v>1943</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" spans="1:8">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" spans="1:6">
       <c r="A107" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>1999</v>
+        <v>1945</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>2000</v>
+        <v>1946</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1907</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="4" t="s">
-        <v>1742</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>30</v>
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>2002</v>
+        <v>1948</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>2003</v>
+        <v>1949</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>2004</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="4" t="s">
         <v>36</v>
       </c>
@@ -24711,25 +23721,19 @@
         <v>17</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>2006</v>
+        <v>1951</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>2007</v>
+        <v>1952</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>2008</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H109" s="4" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="4" t="s">
         <v>36</v>
       </c>
@@ -24737,25 +23741,19 @@
         <v>17</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>2010</v>
+        <v>1954</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>2011</v>
+        <v>1955</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>2012</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="4" t="s">
         <v>16</v>
       </c>
@@ -24763,51 +23761,39 @@
         <v>56</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>2014</v>
+        <v>1957</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>2015</v>
+        <v>1958</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>2016</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="112" s="1" customFormat="1" spans="1:8">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" spans="1:6">
       <c r="A112" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>2018</v>
+        <v>1960</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>2019</v>
+        <v>1961</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>2020</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="4" t="s">
         <v>16</v>
       </c>
@@ -24815,25 +23801,19 @@
         <v>56</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>2022</v>
+        <v>1963</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>2023</v>
+        <v>1964</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>2024</v>
-      </c>
-      <c r="G113" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H113" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="4" t="s">
         <v>16</v>
       </c>
@@ -24841,25 +23821,19 @@
         <v>56</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>2025</v>
+        <v>1965</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>2023</v>
+        <v>1964</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>2026</v>
-      </c>
-      <c r="G114" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H114" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="4" t="s">
         <v>36</v>
       </c>
@@ -24867,25 +23841,19 @@
         <v>17</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>2027</v>
+        <v>1966</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>2028</v>
+        <v>1967</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>2029</v>
+        <v>1968</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>2030</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>2031</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="4" t="s">
         <v>16</v>
       </c>
@@ -24893,25 +23861,19 @@
         <v>56</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>2033</v>
+        <v>1970</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>2034</v>
+        <v>1971</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>2035</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>2036</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="4" t="s">
         <v>16</v>
       </c>
@@ -24922,22 +23884,16 @@
         <v>1313</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>2038</v>
+        <v>1973</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>2039</v>
+        <v>1974</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>2041</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="4" t="s">
         <v>36</v>
       </c>
@@ -24945,25 +23901,19 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>2043</v>
+        <v>1976</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>2044</v>
+        <v>1977</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="4" t="s">
         <v>36</v>
       </c>
@@ -24974,22 +23924,16 @@
         <v>21</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>2046</v>
+        <v>1979</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>2047</v>
+        <v>1980</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="4" t="s">
         <v>36</v>
       </c>
@@ -25000,22 +23944,16 @@
         <v>21</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>2049</v>
+        <v>1982</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>2050</v>
+        <v>1983</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="4" t="s">
         <v>16</v>
       </c>
@@ -25023,25 +23961,19 @@
         <v>17</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>2052</v>
+        <v>1985</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>2053</v>
+        <v>1986</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>2054</v>
+        <v>1987</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="4" t="s">
         <v>16</v>
       </c>
@@ -25055,19 +23987,13 @@
         <v>1200</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>2056</v>
+        <v>1989</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>2057</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H122" s="4" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:6">
       <c r="A123" s="4" t="s">
         <v>36</v>
       </c>
@@ -25075,25 +24001,19 @@
         <v>17</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>2058</v>
+        <v>1990</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>2059</v>
+        <v>1991</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="4" t="s">
         <v>36</v>
       </c>
@@ -25104,100 +24024,76 @@
         <v>21</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>2062</v>
+        <v>1993</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>2063</v>
+        <v>1994</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="125" s="1" customFormat="1" spans="1:8">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="1" spans="1:6">
       <c r="A125" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>2065</v>
+        <v>1996</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>2066</v>
+        <v>1997</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>2067</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>2068</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="126" s="1" customFormat="1" spans="1:8">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="126" s="1" customFormat="1" spans="1:6">
       <c r="A126" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>2070</v>
+        <v>1999</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>2071</v>
+        <v>2000</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>2072</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>2073</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="127" s="1" customFormat="1" spans="1:8">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="127" s="1" customFormat="1" spans="1:6">
       <c r="A127" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>2075</v>
+        <v>2002</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>2071</v>
+        <v>2000</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>2072</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>2076</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="4" t="s">
         <v>36</v>
       </c>
@@ -25208,22 +24104,16 @@
         <v>21</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>2077</v>
+        <v>2003</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>2078</v>
+        <v>2004</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="4" t="s">
         <v>36</v>
       </c>
@@ -25234,22 +24124,16 @@
         <v>21</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>2080</v>
+        <v>2006</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>2081</v>
+        <v>2007</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
         <v>36</v>
       </c>
@@ -25260,48 +24144,36 @@
         <v>21</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>2082</v>
+        <v>2008</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>1819</v>
+        <v>1799</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>2083</v>
-      </c>
-      <c r="G130" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H130" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="131" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="131" s="1" customFormat="1" spans="1:6">
       <c r="A131" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>2084</v>
+        <v>2009</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>2085</v>
+        <v>2010</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="4" t="s">
         <v>36</v>
       </c>
@@ -25309,25 +24181,19 @@
         <v>17</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>2088</v>
+        <v>2012</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>2089</v>
+        <v>2013</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>2090</v>
+        <v>2014</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>2091</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>2092</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="4" t="s">
         <v>36</v>
       </c>
@@ -25338,22 +24204,16 @@
         <v>21</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>2093</v>
+        <v>2016</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>2094</v>
+        <v>2017</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="4" t="s">
         <v>36</v>
       </c>
@@ -25364,22 +24224,16 @@
         <v>21</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>2096</v>
+        <v>2019</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>2097</v>
+        <v>2020</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>2098</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="4" t="s">
         <v>36</v>
       </c>
@@ -25387,25 +24241,19 @@
         <v>17</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>2100</v>
+        <v>2022</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>2101</v>
+        <v>2023</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>2102</v>
+        <v>2024</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="4" t="s">
         <v>36</v>
       </c>
@@ -25416,74 +24264,56 @@
         <v>21</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>2104</v>
+        <v>2026</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>2105</v>
+        <v>2027</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H136" s="4" t="s">
-        <v>2106</v>
-      </c>
-    </row>
-    <row r="137" s="1" customFormat="1" spans="1:8">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="1" spans="1:6">
       <c r="A137" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>2107</v>
+        <v>2029</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>2108</v>
+        <v>2030</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>2109</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>2110</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="138" s="1" customFormat="1" spans="1:8">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="138" s="1" customFormat="1" spans="1:6">
       <c r="A138" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>2112</v>
+        <v>2032</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>2113</v>
+        <v>2033</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>2114</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H138" s="1" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:6">
       <c r="A139" s="4" t="s">
         <v>16</v>
       </c>
@@ -25494,22 +24324,16 @@
         <v>21</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>2115</v>
+        <v>2034</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>2113</v>
+        <v>2033</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>2114</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H139" s="4" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:6">
       <c r="A140" s="4" t="s">
         <v>36</v>
       </c>
@@ -25520,48 +24344,36 @@
         <v>21</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>2116</v>
+        <v>2035</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>2117</v>
+        <v>2036</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="141" s="1" customFormat="1" spans="1:8">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="141" s="1" customFormat="1" spans="1:6">
       <c r="A141" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>2119</v>
+        <v>2038</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>2120</v>
+        <v>2039</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>2121</v>
+        <v>2040</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>2122</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>2123</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="4" t="s">
         <v>16</v>
       </c>
@@ -25569,25 +24381,19 @@
         <v>56</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>2125</v>
+        <v>2042</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>528</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>2126</v>
+        <v>2043</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>2127</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="4" t="s">
         <v>16</v>
       </c>
@@ -25595,25 +24401,19 @@
         <v>56</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>2129</v>
+        <v>2045</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>2130</v>
+        <v>2046</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>2131</v>
+        <v>2047</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>2132</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>2133</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="4" t="s">
         <v>16</v>
       </c>
@@ -25624,22 +24424,16 @@
         <v>21</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>2135</v>
+        <v>2049</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>2136</v>
+        <v>2050</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G144" s="4" t="s">
-        <v>2137</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="4" t="s">
         <v>16</v>
       </c>
@@ -25647,25 +24441,19 @@
         <v>56</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>2139</v>
+        <v>2052</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>2140</v>
+        <v>2053</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>2141</v>
+        <v>2054</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="4" t="s">
         <v>16</v>
       </c>
@@ -25673,51 +24461,39 @@
         <v>56</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>2143</v>
+        <v>2056</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>2144</v>
+        <v>2057</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>2035</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>2145</v>
-      </c>
-      <c r="H146" s="4" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="147" s="1" customFormat="1" spans="1:8">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="147" s="1" customFormat="1" spans="1:6">
       <c r="A147" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>2147</v>
+        <v>2059</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>2078</v>
+        <v>2004</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>2148</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="4" t="s">
         <v>16</v>
       </c>
@@ -25725,25 +24501,19 @@
         <v>17</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>2150</v>
+        <v>2061</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>2151</v>
+        <v>2062</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>2152</v>
+        <v>2063</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>2153</v>
-      </c>
-      <c r="G148" s="4" t="s">
-        <v>2154</v>
-      </c>
-      <c r="H148" s="4" t="s">
-        <v>2155</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="4" t="s">
         <v>16</v>
       </c>
@@ -25751,25 +24521,19 @@
         <v>17</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>2156</v>
+        <v>2065</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>2157</v>
+        <v>2066</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>1929</v>
+        <v>1891</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>2158</v>
-      </c>
-      <c r="G149" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H149" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="4" t="s">
         <v>16</v>
       </c>
@@ -25780,22 +24544,16 @@
         <v>21</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>2159</v>
+        <v>2067</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>2160</v>
+        <v>2068</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>2161</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="4" t="s">
         <v>36</v>
       </c>
@@ -25806,22 +24564,16 @@
         <v>21</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>2162</v>
+        <v>2070</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>2163</v>
+        <v>2071</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G151" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>2164</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="4" t="s">
         <v>16</v>
       </c>
@@ -25832,48 +24584,36 @@
         <v>21</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>2165</v>
+        <v>2073</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>2166</v>
+        <v>2074</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G152" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="153" s="1" customFormat="1" spans="1:8">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="153" s="1" customFormat="1" spans="1:6">
       <c r="A153" s="1" t="s">
-        <v>1742</v>
+        <v>35</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>2167</v>
+        <v>2075</v>
       </c>
       <c r="E153" s="6" t="s">
         <v>528</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="4" t="s">
         <v>16</v>
       </c>
@@ -25884,22 +24624,16 @@
         <v>21</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>2169</v>
+        <v>2077</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>2170</v>
+        <v>2078</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G154" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" s="4" t="s">
         <v>16</v>
       </c>
@@ -25907,7 +24641,7 @@
         <v>56</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>2172</v>
+        <v>2080</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>427</v>
@@ -25916,16 +24650,10 @@
         <v>430</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>2173</v>
-      </c>
-      <c r="G155" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="H155" s="4" t="s">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" s="4" t="s">
         <v>36</v>
       </c>
@@ -25936,22 +24664,16 @@
         <v>21</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>2176</v>
+        <v>2082</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>2177</v>
+        <v>2083</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>2178</v>
-      </c>
-      <c r="G156" s="4" t="s">
-        <v>2179</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>2180</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" s="4" t="s">
         <v>16</v>
       </c>
@@ -25965,19 +24687,13 @@
         <v>1051</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>2181</v>
+        <v>2085</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>2182</v>
-      </c>
-      <c r="G157" s="4" t="s">
-        <v>2183</v>
-      </c>
-      <c r="H157" s="4" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" s="4" t="s">
         <v>36</v>
       </c>
@@ -25985,25 +24701,19 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>2185</v>
+        <v>2087</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>2186</v>
+        <v>2088</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>2187</v>
+        <v>2089</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>2188</v>
-      </c>
-      <c r="G158" s="4" t="s">
-        <v>2189</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" s="4" t="s">
         <v>36</v>
       </c>
@@ -26011,25 +24721,19 @@
         <v>17</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>2191</v>
+        <v>2091</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>2192</v>
+        <v>2092</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>2193</v>
+        <v>2093</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>2194</v>
-      </c>
-      <c r="G159" s="4" t="s">
-        <v>2195</v>
-      </c>
-      <c r="H159" s="4" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:6">
       <c r="A160" s="4" t="s">
         <v>16</v>
       </c>
@@ -26037,25 +24741,19 @@
         <v>56</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>2196</v>
+        <v>2094</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>2197</v>
+        <v>2095</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>2198</v>
+        <v>2096</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>2199</v>
-      </c>
-      <c r="G160" s="4" t="s">
-        <v>2200</v>
-      </c>
-      <c r="H160" s="4" t="s">
-        <v>2201</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" s="4" t="s">
         <v>16</v>
       </c>
@@ -26066,22 +24764,16 @@
         <v>21</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>2202</v>
+        <v>2098</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>2203</v>
+        <v>2099</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>2204</v>
-      </c>
-      <c r="G161" s="4" t="s">
-        <v>2205</v>
-      </c>
-      <c r="H161" s="4" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" s="4" t="s">
         <v>16</v>
       </c>
@@ -26092,22 +24784,16 @@
         <v>21</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>2206</v>
+        <v>2100</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>2207</v>
+        <v>2101</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>2208</v>
-      </c>
-      <c r="G162" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H162" s="4" t="s">
-        <v>2209</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" s="4" t="s">
         <v>16</v>
       </c>
@@ -26115,25 +24801,19 @@
         <v>56</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>2210</v>
+        <v>2103</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>2211</v>
+        <v>2104</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>2212</v>
+        <v>2105</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>2213</v>
-      </c>
-      <c r="G163" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H163" s="4" t="s">
-        <v>2214</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" s="4" t="s">
         <v>16</v>
       </c>
@@ -26144,46 +24824,36 @@
         <v>21</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>2215</v>
+        <v>2107</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>2216</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G164" s="4" t="s">
-        <v>2217</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>2218</v>
-      </c>
-    </row>
-    <row r="165" s="1" customFormat="1" ht="13.9" spans="1:11">
+        <v>2108</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1" ht="13.9" spans="1:9">
       <c r="A165" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B165" s="8"/>
+      <c r="B165" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="C165" s="9" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>1638</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>2219</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>2220</v>
-      </c>
-      <c r="H165" s="11" t="s">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="166" customFormat="1" spans="1:11">
+        <v>1639</v>
+      </c>
+      <c r="F165" s="11" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" spans="1:9">
       <c r="A166" s="2" t="s">
         <v>16</v>
       </c>
@@ -26194,20 +24864,16 @@
         <v>21</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>2221</v>
+        <v>2110</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>2222</v>
-      </c>
-      <c r="F166" s="4" t="s">
-        <v>2219</v>
-      </c>
-      <c r="G166" s="4"/>
-      <c r="H166" t="s">
-        <v>2223</v>
-      </c>
-    </row>
-    <row r="167" customFormat="1" spans="1:11">
+        <v>2111</v>
+      </c>
+      <c r="F166" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:9">
       <c r="A167" s="2" t="s">
         <v>16</v>
       </c>
@@ -26218,23 +24884,19 @@
         <v>21</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>2224</v>
+        <v>2113</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>2225</v>
+        <v>2114</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>2226</v>
+        <v>2115</v>
       </c>
       <c r="G167" s="4"/>
-      <c r="H167" s="4" t="s">
-        <v>2227</v>
-      </c>
+      <c r="H167" s="4"/>
       <c r="I167" s="4"/>
-      <c r="J167" s="4"/>
-      <c r="K167" s="4"/>
-    </row>
-    <row r="168" customFormat="1" spans="1:11">
+    </row>
+    <row r="168" customFormat="1" spans="1:9">
       <c r="A168" s="2" t="s">
         <v>16</v>
       </c>
@@ -26242,24 +24904,22 @@
         <v>56</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>2228</v>
+        <v>2116</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>1719</v>
-      </c>
-      <c r="F168" s="4"/>
+        <v>1720</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>1718</v>
+      </c>
       <c r="G168" s="4"/>
-      <c r="H168" s="4" t="s">
-        <v>1717</v>
-      </c>
+      <c r="H168" s="4"/>
       <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
-      <c r="K168" s="4"/>
-    </row>
-    <row r="169" customFormat="1" spans="1:11">
+    </row>
+    <row r="169" customFormat="1" spans="1:9">
       <c r="A169" s="2" t="s">
         <v>16</v>
       </c>
@@ -26267,24 +24927,22 @@
         <v>56</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>2229</v>
+        <v>2117</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>1701</v>
-      </c>
-      <c r="F169" s="4"/>
+        <v>1702</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>1700</v>
+      </c>
       <c r="G169" s="4"/>
-      <c r="H169" s="4" t="s">
-        <v>1699</v>
-      </c>
+      <c r="H169" s="4"/>
       <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
-      <c r="K169" s="4"/>
-    </row>
-    <row r="170" customFormat="1" spans="1:11">
+    </row>
+    <row r="170" customFormat="1" spans="1:9">
       <c r="A170" s="2" t="s">
         <v>16</v>
       </c>
@@ -26295,23 +24953,19 @@
         <v>21</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>2230</v>
+        <v>2118</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>2231</v>
+        <v>2119</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>2232</v>
+        <v>2120</v>
       </c>
       <c r="G170" s="4"/>
-      <c r="H170" s="4" t="s">
-        <v>2233</v>
-      </c>
+      <c r="H170" s="4"/>
       <c r="I170" s="4"/>
-      <c r="J170" s="4"/>
-      <c r="K170" s="4"/>
-    </row>
-    <row r="171" customFormat="1" spans="1:11">
+    </row>
+    <row r="171" customFormat="1" spans="1:9">
       <c r="A171" s="2" t="s">
         <v>16</v>
       </c>
@@ -26319,22 +24973,20 @@
         <v>56</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>2234</v>
+        <v>2121</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>2235</v>
+        <v>2122</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>1709</v>
-      </c>
-      <c r="F171" s="4"/>
+        <v>1710</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>1708</v>
+      </c>
       <c r="G171" s="4"/>
-      <c r="H171" s="4" t="s">
-        <v>1707</v>
-      </c>
+      <c r="H171" s="4"/>
       <c r="I171" s="4"/>
-      <c r="J171" s="4"/>
-      <c r="K171" s="4"/>
     </row>
     <row r="172" customFormat="1"/>
     <row r="173" customFormat="1"/>
@@ -26422,21 +25074,44 @@
       <c r="E208" s="16"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H187" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A171 A209:A1048576">
-      <formula1>"是,否,无法确认"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B164 B209:B1048576">
-      <formula1>"持续更新,更新不详,停止更新"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B166:B171">
-      <formula1>"停止更新,持续更新,更新不详"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A7:F7"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="34.5929203539823" customWidth="1"/>
+    <col min="5" max="5" width="15.8849557522124" customWidth="1"/>
+    <col min="6" max="6" width="67.5132743362832" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>